--- a/Deals_Sheet_REL.xlsx
+++ b/Deals_Sheet_REL.xlsx
@@ -1662,9 +1662,8 @@
       <c r="K20" s="121" t="n">
         <v>11</v>
       </c>
-      <c r="L20" s="123">
-        <f>H20/K20</f>
-        <v/>
+      <c r="L20" s="123" t="n">
+        <v>0.4545</v>
       </c>
       <c r="M20" s="120" t="n">
         <v>12</v>
@@ -1809,9 +1808,8 @@
       <c r="K22" s="121" t="n">
         <v>6.5</v>
       </c>
-      <c r="L22" s="123">
-        <f>H22/K22</f>
-        <v/>
+      <c r="L22" s="123" t="n">
+        <v>0.4923</v>
       </c>
       <c r="M22" s="120" t="n">
         <v>12</v>
@@ -2194,9 +2192,8 @@
       <c r="K27" s="121" t="n">
         <v>11</v>
       </c>
-      <c r="L27" s="123">
-        <f>J27/K27</f>
-        <v/>
+      <c r="L27" s="123" t="n">
+        <v>0.62</v>
       </c>
       <c r="M27" s="120" t="n">
         <v>18</v>
@@ -2487,9 +2484,8 @@
       <c r="K31" s="121" t="n">
         <v>2.5</v>
       </c>
-      <c r="L31" s="123">
-        <f>J32/K32</f>
-        <v/>
+      <c r="L31" s="123" t="n">
+        <v>0.38</v>
       </c>
       <c r="M31" s="120" t="n">
         <v>12</v>
@@ -2626,9 +2622,8 @@
       <c r="K33" s="121" t="n">
         <v>148.63</v>
       </c>
-      <c r="L33" s="123">
-        <f>J33/K33</f>
-        <v/>
+      <c r="L33" s="123" t="n">
+        <v>0.6081</v>
       </c>
       <c r="M33" s="120" t="n">
         <v>30</v>
@@ -2701,9 +2696,8 @@
       <c r="K34" s="121" t="n">
         <v>8</v>
       </c>
-      <c r="L34" s="123">
-        <f>J36/K36</f>
-        <v/>
+      <c r="L34" s="123" t="n">
+        <v>0.7</v>
       </c>
       <c r="M34" s="120" t="n">
         <v>18</v>
@@ -2778,9 +2772,8 @@
       <c r="K35" s="121" t="n">
         <v>16.62</v>
       </c>
-      <c r="L35" s="123">
-        <f>J35/K35</f>
-        <v/>
+      <c r="L35" s="123" t="n">
+        <v>0.6498</v>
       </c>
       <c r="M35" s="120" t="n">
         <v>9</v>
@@ -2921,9 +2914,8 @@
       <c r="K37" s="121" t="n">
         <v>8.52</v>
       </c>
-      <c r="L37" s="123">
-        <f>J34/K34</f>
-        <v/>
+      <c r="L37" s="123" t="n">
+        <v>0.8005</v>
       </c>
       <c r="M37" s="120" t="n">
         <v>12</v>
@@ -3807,7 +3799,7 @@
         <v>477.42</v>
       </c>
       <c r="L51" s="131" t="n">
-        <v>0.6237</v>
+        <v>0.6234</v>
       </c>
       <c r="M51" s="159" t="n"/>
       <c r="N51" s="161" t="n"/>

--- a/Deals_Sheet_REL.xlsx
+++ b/Deals_Sheet_REL.xlsx
@@ -10592,19 +10592,19 @@
       <c r="F96" s="159" t="n"/>
       <c r="G96" s="159" t="n"/>
       <c r="H96" s="130">
-        <f>SUM(H5:H19)</f>
+        <f>SUM(H5:H94)</f>
         <v/>
       </c>
       <c r="I96" s="130">
-        <f>SUM(I5:I19)</f>
+        <f>SUM(I5:I94)</f>
         <v/>
       </c>
       <c r="J96" s="130">
-        <f>SUM(J5:J19)</f>
+        <f>SUM(J5:J94)</f>
         <v/>
       </c>
       <c r="K96" s="130">
-        <f>SUM(K5:K19)</f>
+        <f>SUM(K5:K94)</f>
         <v/>
       </c>
       <c r="L96" s="131">
@@ -11185,19 +11185,19 @@
       <c r="F10" s="159" t="n"/>
       <c r="G10" s="159" t="n"/>
       <c r="H10" s="130">
-        <f>SUM(H5:H6)</f>
+        <f>SUM(H5:H8)</f>
         <v/>
       </c>
       <c r="I10" s="130">
-        <f>SUM(I5:I6)</f>
+        <f>SUM(I5:I8)</f>
         <v/>
       </c>
       <c r="J10" s="130">
-        <f>SUM(J5:J6)</f>
+        <f>SUM(J5:J8)</f>
         <v/>
       </c>
       <c r="K10" s="130">
-        <f>SUM(K5:K6)</f>
+        <f>SUM(K5:K8)</f>
         <v/>
       </c>
       <c r="L10" s="131">

--- a/Deals_Sheet_REL.xlsx
+++ b/Deals_Sheet_REL.xlsx
@@ -1227,7 +1227,11 @@
           <t>Comments</t>
         </is>
       </c>
-      <c r="S7" s="119" t="n"/>
+      <c r="S7" s="119" t="inlineStr">
+        <is>
+          <t>REL Share (£m)</t>
+        </is>
+      </c>
       <c r="T7" s="107" t="n"/>
       <c r="U7" s="107" t="n"/>
       <c r="V7" s="107" t="n"/>
@@ -1611,7 +1615,11 @@
           <t>Comments</t>
         </is>
       </c>
-      <c r="S19" s="119" t="n"/>
+      <c r="S19" s="119" t="inlineStr">
+        <is>
+          <t>REL Share (£m)</t>
+        </is>
+      </c>
       <c r="T19" s="107" t="n"/>
       <c r="U19" s="107" t="n"/>
       <c r="V19" s="107" t="n"/>
@@ -10634,7 +10642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A3:X10"/>
+  <dimension ref="A3:X17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.70703125" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="39.28" customWidth="1" style="167" min="1" max="1"/>
@@ -10645,7 +10653,7 @@
     <row r="3" ht="28.5" customFormat="1" customHeight="1" s="98">
       <c r="A3" s="168" t="inlineStr">
         <is>
-          <t>Completed Deals</t>
+          <t>Redeemed Loans</t>
         </is>
       </c>
       <c r="B3" s="110" t="n"/>
@@ -10773,6 +10781,16 @@
           <t>Comments</t>
         </is>
       </c>
+      <c r="U4" s="0" t="inlineStr">
+        <is>
+          <t>Introducer</t>
+        </is>
+      </c>
+      <c r="V4" s="0" t="inlineStr">
+        <is>
+          <t>REL Share (£mn)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="12.75" customFormat="1" customHeight="1" s="98">
       <c r="A5" s="108" t="inlineStr">
@@ -10790,7 +10808,7 @@
       </c>
       <c r="D5" s="108" t="inlineStr">
         <is>
-          <t>GMP Limited</t>
+          <t>Giant Mind UK Ltd (Cohort)</t>
         </is>
       </c>
       <c r="E5" s="120" t="inlineStr">
@@ -10812,7 +10830,7 @@
         <v>4.214</v>
       </c>
       <c r="I5" s="122" t="n">
-        <v>0.967</v>
+        <v>1.003</v>
       </c>
       <c r="J5" s="121" t="n">
         <v>4.43</v>
@@ -10831,7 +10849,7 @@
       </c>
       <c r="O5" s="120" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>Jun 2023</t>
         </is>
       </c>
       <c r="P5" s="120" t="inlineStr">
@@ -10846,7 +10864,7 @@
       </c>
       <c r="R5" s="120" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S5" s="108" t="inlineStr">
@@ -10856,7 +10874,7 @@
       </c>
       <c r="T5" s="108" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Redeemed 15/12/24 (Appold St). Whole loan £21.07m with Cohort; REL share £4.214m.</t>
         </is>
       </c>
       <c r="U5" s="195" t="inlineStr">
@@ -10864,27 +10882,27 @@
           <t>Alexey</t>
         </is>
       </c>
-      <c r="V5" s="107" t="n"/>
+      <c r="V5" s="107" t="n">
+        <v>4.214</v>
+      </c>
       <c r="W5" s="107" t="n"/>
       <c r="X5" s="107" t="n"/>
     </row>
     <row r="6" ht="12.75" customFormat="1" customHeight="1" s="98">
       <c r="A6" s="108" t="inlineStr">
         <is>
-          <t>Sunderland Doxford</t>
-        </is>
-      </c>
-      <c r="B6" s="157" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="C6" s="120" t="n">
-        <v>1</v>
-      </c>
+          <t>72 Park St</t>
+        </is>
+      </c>
+      <c r="B6" s="129" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="C6" s="120" t="n"/>
       <c r="D6" s="108" t="inlineStr">
         <is>
-          <t>Rasmala</t>
+          <t>SSK 72 PS Limited (Icewell)</t>
         </is>
       </c>
       <c r="E6" s="120" t="inlineStr">
@@ -10903,37 +10921,30 @@
         </is>
       </c>
       <c r="H6" s="121" t="n">
-        <v>4</v>
+        <v>2.24</v>
       </c>
       <c r="I6" s="122" t="n">
-        <v>0.85</v>
+        <v>0.524</v>
       </c>
       <c r="J6" s="121" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="K6" s="121" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="L6" s="123">
-        <f>J6/K6</f>
-        <v/>
+        <v>8</v>
+      </c>
+      <c r="L6" s="123" t="n">
+        <v>0.7</v>
       </c>
       <c r="M6" s="120" t="n">
-        <v>24</v>
-      </c>
-      <c r="N6" s="124" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="O6" s="124" t="inlineStr">
-        <is>
-          <t>July</t>
-        </is>
-      </c>
-      <c r="P6" s="124" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="N6" s="124" t="n"/>
+      <c r="O6" s="120" t="inlineStr">
+        <is>
+          <t>Mar 2024</t>
+        </is>
+      </c>
+      <c r="P6" s="120" t="n"/>
       <c r="Q6" s="125" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -10951,35 +10962,31 @@
       </c>
       <c r="T6" s="108" t="inlineStr">
         <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="U6" s="196" t="inlineStr">
-        <is>
-          <t>Mantra</t>
-        </is>
-      </c>
-      <c r="V6" s="107" t="n"/>
+          <t>Redeemed 04/12/24. Whole loan £5.6m with Icewell; REL share £2.24m. Asset class TBC.</t>
+        </is>
+      </c>
+      <c r="U6" s="195" t="n"/>
+      <c r="V6" s="107" t="n">
+        <v>2.24</v>
+      </c>
       <c r="W6" s="107" t="n"/>
       <c r="X6" s="107" t="n"/>
     </row>
     <row r="7" ht="12.75" customFormat="1" customHeight="1" s="98">
-      <c r="A7" s="155" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B7" s="108" t="inlineStr">
-        <is>
-          <t>Uxbridge</t>
-        </is>
-      </c>
-      <c r="C7" s="120" t="inlineStr">
-        <is>
-          <t>Mixed Use</t>
-        </is>
-      </c>
+      <c r="A7" s="108" t="inlineStr">
+        <is>
+          <t>Grove / Hick</t>
+        </is>
+      </c>
+      <c r="B7" s="129" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="C7" s="120" t="n"/>
       <c r="D7" s="108" t="inlineStr">
         <is>
-          <t>DNA Property Partners</t>
+          <t>RAK Assets Limited</t>
         </is>
       </c>
       <c r="E7" s="120" t="inlineStr">
@@ -10998,80 +11005,74 @@
         </is>
       </c>
       <c r="H7" s="121" t="n">
-        <v>8.199999999999999</v>
+        <v>3.5775</v>
       </c>
       <c r="I7" s="122" t="n">
-        <v>1.69</v>
+        <v>0.579</v>
       </c>
       <c r="J7" s="121" t="n">
-        <v>8.199999999999999</v>
+        <v>3.5775</v>
       </c>
       <c r="K7" s="121" t="n">
-        <v>14</v>
-      </c>
-      <c r="L7" s="123">
-        <f>J7/K7</f>
-        <v/>
+        <v>6.345</v>
+      </c>
+      <c r="L7" s="123" t="n">
+        <v>0.5638</v>
       </c>
       <c r="M7" s="120" t="n">
-        <v>18</v>
-      </c>
-      <c r="N7" s="124" t="n">
-        <v>0.1458</v>
-      </c>
-      <c r="O7" s="125" t="inlineStr">
-        <is>
-          <t>Aug</t>
-        </is>
-      </c>
-      <c r="P7" s="120" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="N7" s="124" t="n"/>
+      <c r="O7" s="120" t="inlineStr">
+        <is>
+          <t>Apr 2024</t>
+        </is>
+      </c>
+      <c r="P7" s="120" t="n"/>
       <c r="Q7" s="125" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="R7" s="108" t="inlineStr">
+      <c r="R7" s="120" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S7" s="98" t="inlineStr">
+      <c r="S7" s="108" t="inlineStr">
         <is>
           <t>Broker</t>
         </is>
       </c>
       <c r="T7" s="108" t="inlineStr">
         <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="U7" s="98" t="inlineStr">
-        <is>
-          <t>Jay Bohgal</t>
-        </is>
-      </c>
+          <t>Redeemed 25/07/25. REL sole lender, no syndication partner.</t>
+        </is>
+      </c>
+      <c r="U7" s="195" t="n"/>
+      <c r="V7" s="107" t="n">
+        <v>3.5775</v>
+      </c>
+      <c r="W7" s="107" t="n"/>
+      <c r="X7" s="107" t="n"/>
     </row>
     <row r="8" ht="12.75" customFormat="1" customHeight="1" s="98">
-      <c r="A8" s="155" t="n">
-        <v>45809</v>
-      </c>
-      <c r="B8" s="108" t="inlineStr">
-        <is>
-          <t>Stanmore</t>
-        </is>
-      </c>
-      <c r="C8" s="120" t="inlineStr">
-        <is>
-          <t>Retirement living</t>
-        </is>
+      <c r="A8" s="108" t="inlineStr">
+        <is>
+          <t>Sunderland Doxford</t>
+        </is>
+      </c>
+      <c r="B8" s="129" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="C8" s="120" t="n">
+        <v>1</v>
       </c>
       <c r="D8" s="108" t="inlineStr">
         <is>
-          <t>Elysian Group</t>
+          <t>Oryx 2 Real Estate (Oak North)</t>
         </is>
       </c>
       <c r="E8" s="120" t="inlineStr">
@@ -11090,35 +11091,34 @@
         </is>
       </c>
       <c r="H8" s="121" t="n">
-        <v>17.55</v>
+        <v>1.3125</v>
       </c>
       <c r="I8" s="122" t="n">
-        <v>0.518</v>
+        <v>0.541</v>
       </c>
       <c r="J8" s="121" t="n">
-        <v>17.55</v>
+        <v>3.75</v>
       </c>
       <c r="K8" s="121" t="n">
-        <v>24.035</v>
-      </c>
-      <c r="L8" s="123">
-        <f>J8/K8</f>
-        <v/>
+        <v>6.25</v>
+      </c>
+      <c r="L8" s="123" t="n">
+        <v>0.6</v>
       </c>
       <c r="M8" s="120" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N8" s="124" t="n">
-        <v>0.2511</v>
-      </c>
-      <c r="O8" s="125" t="inlineStr">
-        <is>
-          <t>Sep</t>
+        <v>0.133</v>
+      </c>
+      <c r="O8" s="120" t="inlineStr">
+        <is>
+          <t>Oct 2023</t>
         </is>
       </c>
       <c r="P8" s="120" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="Q8" s="125" t="inlineStr">
@@ -11126,26 +11126,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="R8" s="108" t="inlineStr">
+      <c r="R8" s="120" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S8" s="98" t="inlineStr">
-        <is>
-          <t>Direct</t>
+      <c r="S8" s="108" t="inlineStr">
+        <is>
+          <t>Broker</t>
         </is>
       </c>
       <c r="T8" s="108" t="inlineStr">
         <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="U8" s="98" t="inlineStr">
-        <is>
-          <t>Deepesh</t>
-        </is>
-      </c>
+          <t>Redeemed 09/03/26. Whole loan £3.75m with Oak North; REL share £1.3125m. Supersedes the earlier £4.0m figure, which did not match the forecast model.</t>
+        </is>
+      </c>
+      <c r="U8" s="195" t="inlineStr">
+        <is>
+          <t>Mantra</t>
+        </is>
+      </c>
+      <c r="V8" s="107" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="W8" s="107" t="n"/>
+      <c r="X8" s="107" t="n"/>
     </row>
     <row r="9" ht="12.75" customFormat="1" customHeight="1" s="98">
       <c r="A9" s="108" t="n"/>
@@ -11175,7 +11180,7 @@
     <row r="10" ht="12.75" customFormat="1" customHeight="1" s="98">
       <c r="A10" s="127" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Total (redeemed)</t>
         </is>
       </c>
       <c r="B10" s="159" t="n"/>
@@ -11212,6 +11217,353 @@
       <c r="R10" s="159" t="n"/>
       <c r="S10" s="160" t="n"/>
       <c r="T10" s="160" t="n"/>
+      <c r="V10" s="0">
+        <f>SUM(V5:V8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>DRAWN — NOT YET REDEEMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="111" t="inlineStr">
+        <is>
+          <t>Property Address</t>
+        </is>
+      </c>
+      <c r="B13" s="112" t="inlineStr">
+        <is>
+          <t>Asset Class</t>
+        </is>
+      </c>
+      <c r="C13" s="114" t="inlineStr">
+        <is>
+          <t>No of Units</t>
+        </is>
+      </c>
+      <c r="D13" s="113" t="inlineStr">
+        <is>
+          <t>Borrower/JV Partner</t>
+        </is>
+      </c>
+      <c r="E13" s="114" t="inlineStr">
+        <is>
+          <t>Senior/
+Mezz/ 
+Pref</t>
+        </is>
+      </c>
+      <c r="F13" s="114" t="inlineStr">
+        <is>
+          <t>Deal Type</t>
+        </is>
+      </c>
+      <c r="G13" s="114" t="n"/>
+      <c r="H13" s="115" t="inlineStr">
+        <is>
+          <t>Net Loan (£mn)</t>
+        </is>
+      </c>
+      <c r="I13" s="116" t="inlineStr">
+        <is>
+          <t>REL Return 
+(£mn)</t>
+        </is>
+      </c>
+      <c r="J13" s="115" t="inlineStr">
+        <is>
+          <t>Gross Loan (£mn)</t>
+        </is>
+      </c>
+      <c r="K13" s="115" t="inlineStr">
+        <is>
+          <t>Collateral Value (£mn)</t>
+        </is>
+      </c>
+      <c r="L13" s="117" t="inlineStr">
+        <is>
+          <t>LTV</t>
+        </is>
+      </c>
+      <c r="M13" s="114" t="inlineStr">
+        <is>
+          <t>Length (Months)</t>
+        </is>
+      </c>
+      <c r="N13" s="118" t="inlineStr">
+        <is>
+          <t>IRR 
+Return</t>
+        </is>
+      </c>
+      <c r="O13" s="118" t="inlineStr">
+        <is>
+          <t>Likely timing of drawdown</t>
+        </is>
+      </c>
+      <c r="P13" s="118" t="inlineStr">
+        <is>
+          <t>PG/
+Additional Security</t>
+        </is>
+      </c>
+      <c r="Q13" s="114" t="inlineStr">
+        <is>
+          <t>Term Sheet Issued</t>
+        </is>
+      </c>
+      <c r="R13" s="114" t="inlineStr">
+        <is>
+          <t>Commitment Fee Received</t>
+        </is>
+      </c>
+      <c r="S13" s="113" t="inlineStr">
+        <is>
+          <t>Broker / Direct</t>
+        </is>
+      </c>
+      <c r="T13" s="113" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="U13" s="0" t="inlineStr">
+        <is>
+          <t>Introducer</t>
+        </is>
+      </c>
+      <c r="V13" s="0" t="inlineStr">
+        <is>
+          <t>REL Share (£mn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="108" t="inlineStr">
+        <is>
+          <t>Uxbridge</t>
+        </is>
+      </c>
+      <c r="B14" s="129" t="inlineStr">
+        <is>
+          <t>Mixed Use</t>
+        </is>
+      </c>
+      <c r="C14" s="120" t="n">
+        <v>481</v>
+      </c>
+      <c r="D14" s="108" t="inlineStr">
+        <is>
+          <t>DNA Property Partners</t>
+        </is>
+      </c>
+      <c r="E14" s="120" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="F14" s="120" t="inlineStr">
+        <is>
+          <t>Bridge</t>
+        </is>
+      </c>
+      <c r="G14" s="120" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H14" s="121" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I14" s="122" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J14" s="121" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K14" s="121" t="n">
+        <v>14</v>
+      </c>
+      <c r="L14" s="123" t="n">
+        <v>0.5857</v>
+      </c>
+      <c r="M14" s="120" t="n">
+        <v>12</v>
+      </c>
+      <c r="N14" s="124" t="n">
+        <v>0.1469</v>
+      </c>
+      <c r="O14" s="120" t="inlineStr">
+        <is>
+          <t>Aug 2025</t>
+        </is>
+      </c>
+      <c r="P14" s="120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q14" s="125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R14" s="120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S14" s="108" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="T14" s="108" t="inlineStr">
+        <is>
+          <t>Drew 01/08/25 on a 12-month term. NOT redeemed — past maturity 31/07/26, default / extension underway; model now runs to 31/07/27. Whole loan £8.2m with GB Bank; REL share £2.05m.</t>
+        </is>
+      </c>
+      <c r="U14" s="195" t="inlineStr">
+        <is>
+          <t>Jay Bohgal</t>
+        </is>
+      </c>
+      <c r="V14" s="107" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W14" s="107" t="n"/>
+      <c r="X14" s="107" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="108" t="inlineStr">
+        <is>
+          <t>Stanmore</t>
+        </is>
+      </c>
+      <c r="B15" s="129" t="inlineStr">
+        <is>
+          <t>Retirement living</t>
+        </is>
+      </c>
+      <c r="C15" s="120" t="n">
+        <v>23</v>
+      </c>
+      <c r="D15" s="108" t="inlineStr">
+        <is>
+          <t>Elysian Group (Oak North)</t>
+        </is>
+      </c>
+      <c r="E15" s="120" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="F15" s="120" t="inlineStr">
+        <is>
+          <t>Bridge</t>
+        </is>
+      </c>
+      <c r="G15" s="120" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H15" s="121" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="I15" s="122" t="n">
+        <v>2.244</v>
+      </c>
+      <c r="J15" s="121" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="K15" s="121" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="L15" s="123" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="M15" s="120" t="n">
+        <v>15</v>
+      </c>
+      <c r="N15" s="124" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="O15" s="120" t="inlineStr">
+        <is>
+          <t>Sep 2025</t>
+        </is>
+      </c>
+      <c r="P15" s="120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q15" s="125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R15" s="120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S15" s="108" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="T15" s="108" t="inlineStr">
+        <is>
+          <t>Drew 17/09/25 on a 15-month term. NOT redeemed — amortising via unit sales, balance £15.63m, model runs to 17/03/27. Syndicated with Oak North; REL share ~£4.38m derived from the ON LTV, not stated directly — CONFIRM.</t>
+        </is>
+      </c>
+      <c r="U15" s="195" t="inlineStr">
+        <is>
+          <t>Deepesh</t>
+        </is>
+      </c>
+      <c r="V15" s="107" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="W15" s="107" t="n"/>
+      <c r="X15" s="107" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>Total (drawn)</t>
+        </is>
+      </c>
+      <c r="H17" s="0">
+        <f>SUM(H14:H15)</f>
+        <v/>
+      </c>
+      <c r="I17" s="0">
+        <f>SUM(I14:I15)</f>
+        <v/>
+      </c>
+      <c r="J17" s="0">
+        <f>SUM(J14:J15)</f>
+        <v/>
+      </c>
+      <c r="K17" s="0">
+        <f>SUM(K14:K15)</f>
+        <v/>
+      </c>
+      <c r="L17" s="0">
+        <f>J17/K17</f>
+        <v/>
+      </c>
+      <c r="V17" s="0">
+        <f>SUM(V14:V15)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Deals_Sheet_REL.xlsx
+++ b/Deals_Sheet_REL.xlsx
@@ -10642,7 +10642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A3:X17"/>
+  <dimension ref="A3:X20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.70703125" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="39.28" customWidth="1" style="167" min="1" max="1"/>
@@ -11345,20 +11345,18 @@
     <row r="14">
       <c r="A14" s="108" t="inlineStr">
         <is>
-          <t>Uxbridge</t>
+          <t>Palace Green</t>
         </is>
       </c>
       <c r="B14" s="129" t="inlineStr">
         <is>
-          <t>Mixed Use</t>
-        </is>
-      </c>
-      <c r="C14" s="120" t="n">
-        <v>481</v>
-      </c>
+          <t>Resi</t>
+        </is>
+      </c>
+      <c r="C14" s="120" t="n"/>
       <c r="D14" s="108" t="inlineStr">
         <is>
-          <t>DNA Property Partners</t>
+          <t>Ali Ansari (HNW Investor)</t>
         </is>
       </c>
       <c r="E14" s="120" t="inlineStr">
@@ -11377,36 +11375,28 @@
         </is>
       </c>
       <c r="H14" s="121" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I14" s="122" t="n">
-        <v>1.69</v>
-      </c>
+        <v>6.7</v>
+      </c>
+      <c r="I14" s="122" t="n"/>
       <c r="J14" s="121" t="n">
-        <v>8.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="K14" s="121" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="L14" s="123" t="n">
-        <v>0.5857</v>
+        <v>0.406</v>
       </c>
       <c r="M14" s="120" t="n">
         <v>12</v>
       </c>
-      <c r="N14" s="124" t="n">
-        <v>0.1469</v>
-      </c>
+      <c r="N14" s="124" t="n"/>
       <c r="O14" s="120" t="inlineStr">
         <is>
-          <t>Aug 2025</t>
-        </is>
-      </c>
-      <c r="P14" s="120" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Dec 2024</t>
+        </is>
+      </c>
+      <c r="P14" s="120" t="n"/>
       <c r="Q14" s="125" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -11424,16 +11414,16 @@
       </c>
       <c r="T14" s="108" t="inlineStr">
         <is>
-          <t>Drew 01/08/25 on a 12-month term. NOT redeemed — past maturity 31/07/26, default / extension underway; model now runs to 31/07/27. Whole loan £8.2m with GB Bank; REL share £2.05m.</t>
+          <t>Drew 20/12/24, 12-month term, expired 10/09/26. IN DEFAULT — balance accruing, now £7.064m against £6.7m advanced. REL Lendco 3 / HNW Investor. LTV 40.6% net, 54.5% gross on MV £16.5m.</t>
         </is>
       </c>
       <c r="U14" s="195" t="inlineStr">
         <is>
-          <t>Jay Bohgal</t>
+          <t>TBC</t>
         </is>
       </c>
       <c r="V14" s="107" t="n">
-        <v>2.05</v>
+        <v>6.7</v>
       </c>
       <c r="W14" s="107" t="n"/>
       <c r="X14" s="107" t="n"/>
@@ -11441,25 +11431,23 @@
     <row r="15">
       <c r="A15" s="108" t="inlineStr">
         <is>
-          <t>Stanmore</t>
+          <t>St Clements House</t>
         </is>
       </c>
       <c r="B15" s="129" t="inlineStr">
         <is>
-          <t>Retirement living</t>
-        </is>
-      </c>
-      <c r="C15" s="120" t="n">
-        <v>23</v>
-      </c>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="C15" s="120" t="n"/>
       <c r="D15" s="108" t="inlineStr">
         <is>
-          <t>Elysian Group (Oak North)</t>
+          <t>Chart Forte Monument</t>
         </is>
       </c>
       <c r="E15" s="120" t="inlineStr">
         <is>
-          <t>Senior</t>
+          <t>Mezz</t>
         </is>
       </c>
       <c r="F15" s="120" t="inlineStr">
@@ -11473,36 +11461,28 @@
         </is>
       </c>
       <c r="H15" s="121" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="I15" s="122" t="n">
-        <v>2.244</v>
-      </c>
+        <v>23.792</v>
+      </c>
+      <c r="I15" s="122" t="n"/>
       <c r="J15" s="121" t="n">
-        <v>16.64</v>
+        <v>23.792</v>
       </c>
       <c r="K15" s="121" t="n">
-        <v>22.53</v>
+        <v>33.3</v>
       </c>
       <c r="L15" s="123" t="n">
-        <v>0.739</v>
+        <v>0.7145</v>
       </c>
       <c r="M15" s="120" t="n">
-        <v>15</v>
-      </c>
-      <c r="N15" s="124" t="n">
-        <v>0.123</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="N15" s="124" t="n"/>
       <c r="O15" s="120" t="inlineStr">
         <is>
-          <t>Sep 2025</t>
-        </is>
-      </c>
-      <c r="P15" s="120" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+          <t>Dec 2024</t>
+        </is>
+      </c>
+      <c r="P15" s="120" t="n"/>
       <c r="Q15" s="125" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -11515,53 +11495,331 @@
       </c>
       <c r="S15" s="108" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Broker</t>
         </is>
       </c>
       <c r="T15" s="108" t="inlineStr">
         <is>
-          <t>Drew 17/09/25 on a 15-month term. NOT redeemed — amortising via unit sales, balance £15.63m, model runs to 17/03/27. Syndicated with Oak North; REL share ~£4.38m derived from the ON LTV, not stated directly — CONFIRM.</t>
+          <t>Drew 16/12/24, 18-month term, expired 15/06/26 — PAST MATURITY. REL Finance / Oak North; REL holds the mezz, current balance £2.144m of a £23.792m whole loan.</t>
         </is>
       </c>
       <c r="U15" s="195" t="inlineStr">
         <is>
-          <t>Deepesh</t>
+          <t>TBC</t>
         </is>
       </c>
       <c r="V15" s="107" t="n">
-        <v>4.38</v>
+        <v>2.144</v>
       </c>
       <c r="W15" s="107" t="n"/>
       <c r="X15" s="107" t="n"/>
     </row>
+    <row r="16">
+      <c r="A16" s="108" t="inlineStr">
+        <is>
+          <t>Uxbridge</t>
+        </is>
+      </c>
+      <c r="B16" s="129" t="inlineStr">
+        <is>
+          <t>Mixed Use</t>
+        </is>
+      </c>
+      <c r="C16" s="120" t="n">
+        <v>481</v>
+      </c>
+      <c r="D16" s="108" t="inlineStr">
+        <is>
+          <t>DNA Property Partners</t>
+        </is>
+      </c>
+      <c r="E16" s="120" t="inlineStr">
+        <is>
+          <t>Mezz</t>
+        </is>
+      </c>
+      <c r="F16" s="120" t="inlineStr">
+        <is>
+          <t>Bridge</t>
+        </is>
+      </c>
+      <c r="G16" s="120" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H16" s="121" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I16" s="122" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J16" s="121" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K16" s="121" t="n">
+        <v>14</v>
+      </c>
+      <c r="L16" s="123" t="n">
+        <v>0.5857</v>
+      </c>
+      <c r="M16" s="120" t="n">
+        <v>12</v>
+      </c>
+      <c r="N16" s="124" t="n">
+        <v>0.1469</v>
+      </c>
+      <c r="O16" s="120" t="inlineStr">
+        <is>
+          <t>Aug 2025</t>
+        </is>
+      </c>
+      <c r="P16" s="120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q16" s="125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R16" s="120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S16" s="108" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="T16" s="108" t="inlineStr">
+        <is>
+          <t>Drew 01/08/25, 12-month term. NOT redeemed — past maturity 31/07/26, default / extension underway; model runs to 31/07/27. REL Lendco 4 / GB Bank; REL holds the mezz £2.05m of an £8.2m whole loan.</t>
+        </is>
+      </c>
+      <c r="U16" s="195" t="inlineStr">
+        <is>
+          <t>Jay Bohgal</t>
+        </is>
+      </c>
+      <c r="V16" s="107" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W16" s="107" t="n"/>
+      <c r="X16" s="107" t="n"/>
+    </row>
     <row r="17">
-      <c r="A17" s="0" t="inlineStr">
+      <c r="A17" s="108" t="inlineStr">
+        <is>
+          <t>Stanmore</t>
+        </is>
+      </c>
+      <c r="B17" s="129" t="inlineStr">
+        <is>
+          <t>Retirement living</t>
+        </is>
+      </c>
+      <c r="C17" s="120" t="n">
+        <v>23</v>
+      </c>
+      <c r="D17" s="108" t="inlineStr">
+        <is>
+          <t>Elysian Stanmore Site</t>
+        </is>
+      </c>
+      <c r="E17" s="120" t="inlineStr">
+        <is>
+          <t>Mezz</t>
+        </is>
+      </c>
+      <c r="F17" s="120" t="inlineStr">
+        <is>
+          <t>Bridge</t>
+        </is>
+      </c>
+      <c r="G17" s="120" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H17" s="121" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="I17" s="122" t="n">
+        <v>2.244</v>
+      </c>
+      <c r="J17" s="121" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="K17" s="121" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="L17" s="123" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="M17" s="120" t="n">
+        <v>15</v>
+      </c>
+      <c r="N17" s="124" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="O17" s="120" t="inlineStr">
+        <is>
+          <t>Sep 2025</t>
+        </is>
+      </c>
+      <c r="P17" s="120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q17" s="125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R17" s="120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S17" s="108" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="T17" s="108" t="inlineStr">
+        <is>
+          <t>Drew 17/09/25, 15-month term to 17/03/27. Amortising via unit sales, whole-loan balance £12.04m. REL Lendco 5 / Oak North; REL mezz £4.39m, current balance £3.195m.</t>
+        </is>
+      </c>
+      <c r="U17" s="195" t="inlineStr">
+        <is>
+          <t>Deepesh</t>
+        </is>
+      </c>
+      <c r="V17" s="107" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="W17" s="107" t="n"/>
+      <c r="X17" s="107" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="108" t="inlineStr">
+        <is>
+          <t>Peninsular House</t>
+        </is>
+      </c>
+      <c r="B18" s="129" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="C18" s="120" t="n"/>
+      <c r="D18" s="108" t="inlineStr">
+        <is>
+          <t>Peninsular House (sponsor JMK)</t>
+        </is>
+      </c>
+      <c r="E18" s="120" t="inlineStr">
+        <is>
+          <t>Mezz</t>
+        </is>
+      </c>
+      <c r="F18" s="120" t="inlineStr">
+        <is>
+          <t>Bridge</t>
+        </is>
+      </c>
+      <c r="G18" s="120" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H18" s="121" t="n">
+        <v>25.025</v>
+      </c>
+      <c r="I18" s="122" t="n"/>
+      <c r="J18" s="121" t="n">
+        <v>25.025</v>
+      </c>
+      <c r="K18" s="121" t="n">
+        <v>35</v>
+      </c>
+      <c r="L18" s="123" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="M18" s="120" t="n">
+        <v>24</v>
+      </c>
+      <c r="N18" s="124" t="n"/>
+      <c r="O18" s="120" t="inlineStr">
+        <is>
+          <t>Mar 2026</t>
+        </is>
+      </c>
+      <c r="P18" s="120" t="n"/>
+      <c r="Q18" s="125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R18" s="120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S18" s="108" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="T18" s="108" t="inlineStr">
+        <is>
+          <t>Drew 13/03/26, 24-month term to 12/03/28. Newest loan. REL Finance / Oak North; REL mezz £3.15m of a £25.025m whole loan. LTV 71.5% on MV £35m.</t>
+        </is>
+      </c>
+      <c r="U18" s="195" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="V18" s="107" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="W18" s="107" t="n"/>
+      <c r="X18" s="107" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Total (drawn)</t>
         </is>
       </c>
-      <c r="H17" s="0">
-        <f>SUM(H14:H15)</f>
+      <c r="H20">
+        <f>SUM(H14:H18)</f>
         <v/>
       </c>
-      <c r="I17" s="0">
-        <f>SUM(I14:I15)</f>
+      <c r="I20">
+        <f>SUM(I14:I18)</f>
         <v/>
       </c>
-      <c r="J17" s="0">
-        <f>SUM(J14:J15)</f>
+      <c r="J20">
+        <f>SUM(J14:J18)</f>
         <v/>
       </c>
-      <c r="K17" s="0">
-        <f>SUM(K14:K15)</f>
+      <c r="K20">
+        <f>SUM(K14:K18)</f>
         <v/>
       </c>
-      <c r="L17" s="0">
-        <f>J17/K17</f>
+      <c r="L20">
+        <f>J20/K20</f>
         <v/>
       </c>
-      <c r="V17" s="0">
-        <f>SUM(V14:V15)</f>
+      <c r="V20">
+        <f>SUM(V14:V18)</f>
         <v/>
       </c>
     </row>

--- a/Deals_Sheet_REL.xlsx
+++ b/Deals_Sheet_REL.xlsx
@@ -11153,27 +11153,88 @@
       <c r="X8" s="107" t="n"/>
     </row>
     <row r="9" ht="12.75" customFormat="1" customHeight="1" s="98">
-      <c r="A9" s="108" t="n"/>
-      <c r="B9" s="157" t="n"/>
+      <c r="A9" s="108" t="inlineStr">
+        <is>
+          <t>St Clements House</t>
+        </is>
+      </c>
+      <c r="B9" s="129" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
       <c r="C9" s="120" t="n"/>
-      <c r="D9" s="108" t="n"/>
-      <c r="E9" s="120" t="n"/>
-      <c r="F9" s="120" t="n"/>
-      <c r="G9" s="120" t="n"/>
-      <c r="H9" s="121" t="n"/>
+      <c r="D9" s="108" t="inlineStr">
+        <is>
+          <t>Chart Forte Monument</t>
+        </is>
+      </c>
+      <c r="E9" s="120" t="inlineStr">
+        <is>
+          <t>Mezz</t>
+        </is>
+      </c>
+      <c r="F9" s="120" t="inlineStr">
+        <is>
+          <t>Bridge</t>
+        </is>
+      </c>
+      <c r="G9" s="120" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H9" s="121" t="n">
+        <v>23.792</v>
+      </c>
       <c r="I9" s="122" t="n"/>
-      <c r="J9" s="121" t="n"/>
-      <c r="K9" s="121" t="n"/>
-      <c r="L9" s="123" t="n"/>
-      <c r="M9" s="120" t="n"/>
+      <c r="J9" s="121" t="n">
+        <v>23.792</v>
+      </c>
+      <c r="K9" s="121" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="L9" s="123" t="n">
+        <v>0.7145</v>
+      </c>
+      <c r="M9" s="120" t="n">
+        <v>18</v>
+      </c>
       <c r="N9" s="124" t="n"/>
-      <c r="O9" s="124" t="n"/>
-      <c r="P9" s="124" t="n"/>
-      <c r="Q9" s="125" t="n"/>
-      <c r="R9" s="120" t="n"/>
-      <c r="S9" s="108" t="n"/>
-      <c r="U9" s="195" t="n"/>
-      <c r="V9" s="107" t="n"/>
+      <c r="O9" s="120" t="inlineStr">
+        <is>
+          <t>Dec 2024</t>
+        </is>
+      </c>
+      <c r="P9" s="120" t="n"/>
+      <c r="Q9" s="125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R9" s="120" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S9" s="108" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="T9" s="108" t="inlineStr">
+        <is>
+          <t>Redeemed 2026. Drew 16/12/24 on an 18-month term. REL Finance / Oak North; REL held the mezz, £2.144m of a £23.792m whole loan.</t>
+        </is>
+      </c>
+      <c r="U9" s="195" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="V9" s="107" t="n">
+        <v>2.144</v>
+      </c>
       <c r="W9" s="107" t="n"/>
       <c r="X9" s="107" t="n"/>
     </row>
@@ -11190,19 +11251,19 @@
       <c r="F10" s="159" t="n"/>
       <c r="G10" s="159" t="n"/>
       <c r="H10" s="130">
-        <f>SUM(H5:H8)</f>
+        <f>SUM(H5:H9)</f>
         <v/>
       </c>
       <c r="I10" s="130">
-        <f>SUM(I5:I8)</f>
+        <f>SUM(I5:I9)</f>
         <v/>
       </c>
       <c r="J10" s="130">
-        <f>SUM(J5:J8)</f>
+        <f>SUM(J5:J9)</f>
         <v/>
       </c>
       <c r="K10" s="130">
-        <f>SUM(K5:K8)</f>
+        <f>SUM(K5:K9)</f>
         <v/>
       </c>
       <c r="L10" s="131">
@@ -11218,7 +11279,7 @@
       <c r="S10" s="160" t="n"/>
       <c r="T10" s="160" t="n"/>
       <c r="V10" s="0">
-        <f>SUM(V5:V8)</f>
+        <f>SUM(V5:V9)</f>
         <v/>
       </c>
     </row>
@@ -11429,88 +11490,28 @@
       <c r="X14" s="107" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="108" t="inlineStr">
-        <is>
-          <t>St Clements House</t>
-        </is>
-      </c>
-      <c r="B15" s="129" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
+      <c r="A15" s="108" t="n"/>
+      <c r="B15" s="129" t="n"/>
       <c r="C15" s="120" t="n"/>
-      <c r="D15" s="108" t="inlineStr">
-        <is>
-          <t>Chart Forte Monument</t>
-        </is>
-      </c>
-      <c r="E15" s="120" t="inlineStr">
-        <is>
-          <t>Mezz</t>
-        </is>
-      </c>
-      <c r="F15" s="120" t="inlineStr">
-        <is>
-          <t>Bridge</t>
-        </is>
-      </c>
-      <c r="G15" s="120" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H15" s="121" t="n">
-        <v>23.792</v>
-      </c>
+      <c r="D15" s="108" t="n"/>
+      <c r="E15" s="120" t="n"/>
+      <c r="F15" s="120" t="n"/>
+      <c r="G15" s="120" t="n"/>
+      <c r="H15" s="121" t="n"/>
       <c r="I15" s="122" t="n"/>
-      <c r="J15" s="121" t="n">
-        <v>23.792</v>
-      </c>
-      <c r="K15" s="121" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="L15" s="123" t="n">
-        <v>0.7145</v>
-      </c>
-      <c r="M15" s="120" t="n">
-        <v>18</v>
-      </c>
+      <c r="J15" s="121" t="n"/>
+      <c r="K15" s="121" t="n"/>
+      <c r="L15" s="123" t="n"/>
+      <c r="M15" s="120" t="n"/>
       <c r="N15" s="124" t="n"/>
-      <c r="O15" s="120" t="inlineStr">
-        <is>
-          <t>Dec 2024</t>
-        </is>
-      </c>
+      <c r="O15" s="120" t="n"/>
       <c r="P15" s="120" t="n"/>
-      <c r="Q15" s="125" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R15" s="120" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S15" s="108" t="inlineStr">
-        <is>
-          <t>Broker</t>
-        </is>
-      </c>
-      <c r="T15" s="108" t="inlineStr">
-        <is>
-          <t>Drew 16/12/24, 18-month term, expired 15/06/26 — PAST MATURITY. REL Finance / Oak North; REL holds the mezz, current balance £2.144m of a £23.792m whole loan.</t>
-        </is>
-      </c>
-      <c r="U15" s="195" t="inlineStr">
-        <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="V15" s="107" t="n">
-        <v>2.144</v>
-      </c>
+      <c r="Q15" s="125" t="n"/>
+      <c r="R15" s="120" t="n"/>
+      <c r="S15" s="108" t="n"/>
+      <c r="T15" s="108" t="n"/>
+      <c r="U15" s="195" t="n"/>
+      <c r="V15" s="107" t="n"/>
       <c r="W15" s="107" t="n"/>
       <c r="X15" s="107" t="n"/>
     </row>
@@ -11793,32 +11794,32 @@
       <c r="X18" s="107" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>Total (drawn)</t>
         </is>
       </c>
-      <c r="H20">
+      <c r="H20" s="0">
         <f>SUM(H14:H18)</f>
         <v/>
       </c>
-      <c r="I20">
+      <c r="I20" s="0">
         <f>SUM(I14:I18)</f>
         <v/>
       </c>
-      <c r="J20">
+      <c r="J20" s="0">
         <f>SUM(J14:J18)</f>
         <v/>
       </c>
-      <c r="K20">
+      <c r="K20" s="0">
         <f>SUM(K14:K18)</f>
         <v/>
       </c>
-      <c r="L20">
+      <c r="L20" s="0">
         <f>J20/K20</f>
         <v/>
       </c>
-      <c r="V20">
+      <c r="V20" s="0">
         <f>SUM(V14:V18)</f>
         <v/>
       </c>

--- a/Deals_Sheet_REL.xlsx
+++ b/Deals_Sheet_REL.xlsx
@@ -1037,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W57"/>
+  <dimension ref="A1:W61"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14.29" customWidth="1" style="98" min="1" max="1"/>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="R27" s="108" t="inlineStr">
         <is>
-          <t>Revised TS 14/07: 62% LTV, £6.82m, 11% fixed, 18m. Awaiting countersigned TS + fee. Broker Jignesh Desai (IPCA).</t>
+          <t>Revised TS issued 10/09 — same terms, refreshed issuance and offer dates. Moove has acquired the asset with its own funds. Chased 15/09 for feedback; no response yet.</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="R40" s="108" t="inlineStr">
         <is>
-          <t>TS in progress: 45 units/190 beds, MV £11.34m, Serco leases; GBB-funded. GLPG. Terms TBC.</t>
+          <t>TS sent 10/09; awaiting countersigned term sheet and commitment fee.</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="R43" s="108" t="inlineStr">
         <is>
-          <t>Terms 26/08: £10.88m, 68% LTV, 24m @10.35%. RIB/Adam Jaffe. Full TS to follow.</t>
+          <t>TS issued. 09/09 broker reports the client is weighing a cheaper term loan against incoming lettings; REL view is the deal needs transitional funding.</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="R44" s="108" t="inlineStr">
         <is>
-          <t>Terms 28/08: £1.75m, 50% LTV, ~12%, 12m (land). LS Capital/Jason Green. Negotiating price.</t>
+          <t>TS issued. 10/09 broker asked for the full term sheet and advisors; 11/09 REL to send and confirm. Legal fees to stay proportionate to a small loan.</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="R45" s="108" t="inlineStr">
         <is>
-          <t>Neg. 03/09: £13.5m, 60% LTV, 10.5%, 18m; refi of Hilco. Mantra. Competing bid £14m.</t>
+          <t>Updated terms 08/09: £13.5m, 12 months plus a 6-month extension option. 12/09 broker pushing on pricing; REL holding position ahead of formal IC approval.</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="R46" s="108" t="inlineStr">
         <is>
-          <t>Terms 04/09: £7.4m, 65% LTV, 10.75%, £795k IR, 12m. Aquilae/M. Yassin.</t>
+          <t>TS issued. 10/09 broker says the deal is moving forward. 14/09 querying whether REL's 1% fee is inclusive of Aquilae's 1% — REL confirmed it is not.</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="R48" s="108" t="inlineStr">
         <is>
-          <t>NDA 07/09: ~£33m resi land bridge. BLCK. REL to co-lend w/ senior - REL share TBC.</t>
+          <t>NDA 07/09. 08/09 BLCK: sponsor open to taking the land bridge first and raising development finance afterwards, depending on terms.</t>
         </is>
       </c>
     </row>
@@ -3763,97 +3763,365 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="155" t="n"/>
-      <c r="B50" s="108" t="n"/>
-      <c r="C50" s="120" t="n"/>
-      <c r="D50" s="108" t="n"/>
-      <c r="E50" s="120" t="n"/>
-      <c r="F50" s="120" t="n"/>
-      <c r="G50" s="120" t="n"/>
+      <c r="A50" s="155" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B50" s="108" t="inlineStr">
+        <is>
+          <t>Inova Park, Watermead Business Park, Leicester</t>
+        </is>
+      </c>
+      <c r="C50" s="120" t="inlineStr">
+        <is>
+          <t>Industrial / Logistics</t>
+        </is>
+      </c>
+      <c r="D50" s="108" t="inlineStr">
+        <is>
+          <t>Boundary Real Estate Partners (via Moorhall Capital)</t>
+        </is>
+      </c>
+      <c r="E50" s="120" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="F50" s="120" t="inlineStr">
+        <is>
+          <t>Bridge</t>
+        </is>
+      </c>
+      <c r="G50" s="120" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="H50" s="121" t="n"/>
       <c r="I50" s="122" t="n"/>
       <c r="J50" s="121" t="n"/>
-      <c r="K50" s="121" t="n"/>
+      <c r="K50" s="121" t="n">
+        <v>19.4</v>
+      </c>
       <c r="L50" s="123" t="n"/>
       <c r="M50" s="120" t="n"/>
       <c r="N50" s="124" t="n"/>
-      <c r="O50" s="125" t="n"/>
-      <c r="P50" s="120" t="n"/>
-      <c r="Q50" s="108" t="n"/>
-      <c r="R50" s="108" t="n"/>
+      <c r="O50" s="125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P50" s="120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q50" s="108" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="R50" s="108" t="inlineStr">
+        <is>
+          <t>Enquiry 09/09: bridge refi of a consented 61.48-acre industrial site. Gross sought £8-12m (c.40-60% LTV vs £19.4m Colliers MV Feb-26), 12-18m, interest rolled. Repays c.£6m existing. GDV c.£125.3m. Target close Oct-26. Loan amount not yet fixed. Sumeer 14/09: further equity needed if a sale/forward-fund does not complete.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="127" t="inlineStr">
+      <c r="A51" s="155" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B51" s="108" t="inlineStr">
+        <is>
+          <t>32 Featherstone Road (warehouses + pub)</t>
+        </is>
+      </c>
+      <c r="C51" s="120" t="inlineStr">
+        <is>
+          <t>Industrial / Leisure</t>
+        </is>
+      </c>
+      <c r="D51" s="108" t="inlineStr">
+        <is>
+          <t>Neshal &amp; Jaymene Madlani</t>
+        </is>
+      </c>
+      <c r="E51" s="120" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="F51" s="120" t="inlineStr">
+        <is>
+          <t>Bridge</t>
+        </is>
+      </c>
+      <c r="G51" s="120" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H51" s="121" t="n"/>
+      <c r="I51" s="122" t="n"/>
+      <c r="J51" s="121" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K51" s="121" t="n"/>
+      <c r="L51" s="123" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M51" s="120" t="n">
+        <v>24</v>
+      </c>
+      <c r="N51" s="124" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="O51" s="125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P51" s="120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q51" s="108" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="R51" s="108" t="inlineStr">
+        <is>
+          <t>Indicative terms 10/09: £2.25m at 65% LTV, 1% arrangement, 11.5% monthly in arrears, 24m with 9m minimum makewhole. Collateral value TBC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="155" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B52" s="108" t="inlineStr">
+        <is>
+          <t>Amusement Equipment (commercial bridge)</t>
+        </is>
+      </c>
+      <c r="C52" s="120" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="D52" s="108" t="inlineStr">
+        <is>
+          <t>TBC (via Mantra Commercial)</t>
+        </is>
+      </c>
+      <c r="E52" s="120" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="F52" s="120" t="inlineStr">
+        <is>
+          <t>Bridge</t>
+        </is>
+      </c>
+      <c r="G52" s="120" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H52" s="121" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="I52" s="122" t="n"/>
+      <c r="J52" s="121" t="n"/>
+      <c r="K52" s="121" t="n"/>
+      <c r="L52" s="123" t="n"/>
+      <c r="M52" s="120" t="n"/>
+      <c r="N52" s="124" t="n"/>
+      <c r="O52" s="125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P52" s="120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q52" s="108" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="R52" s="108" t="inlineStr">
+        <is>
+          <t>Enquiry 10/09 via Mantra: commercial bridge request, £6.13m net. Property and collateral TBC — request pack attached to the referring email.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="155" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B53" s="108" t="inlineStr">
+        <is>
+          <t>c.£7m enquiry - Elizabeth Donald</t>
+        </is>
+      </c>
+      <c r="C53" s="120" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="D53" s="108" t="inlineStr">
+        <is>
+          <t>Elizabeth Donald (via BPS London)</t>
+        </is>
+      </c>
+      <c r="E53" s="120" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="F53" s="120" t="inlineStr">
+        <is>
+          <t>Bridge</t>
+        </is>
+      </c>
+      <c r="G53" s="120" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H53" s="121" t="n"/>
+      <c r="I53" s="122" t="n"/>
+      <c r="J53" s="121" t="n"/>
+      <c r="K53" s="121" t="n"/>
+      <c r="L53" s="123" t="n"/>
+      <c r="M53" s="120" t="n"/>
+      <c r="N53" s="124" t="n"/>
+      <c r="O53" s="125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P53" s="120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q53" s="108" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="R53" s="108" t="inlineStr">
+        <is>
+          <t>Enquiry 09/09 via Mahir Vachani (BPS London): c.£7m loan. Terms and security TBC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="155" t="n"/>
+      <c r="B54" s="108" t="n"/>
+      <c r="C54" s="120" t="n"/>
+      <c r="D54" s="108" t="n"/>
+      <c r="E54" s="120" t="n"/>
+      <c r="F54" s="120" t="n"/>
+      <c r="G54" s="120" t="n"/>
+      <c r="H54" s="121" t="n"/>
+      <c r="I54" s="122" t="n"/>
+      <c r="J54" s="121" t="n"/>
+      <c r="K54" s="121" t="n"/>
+      <c r="L54" s="123" t="n"/>
+      <c r="M54" s="120" t="n"/>
+      <c r="N54" s="124" t="n"/>
+      <c r="O54" s="125" t="n"/>
+      <c r="P54" s="120" t="n"/>
+      <c r="Q54" s="108" t="n"/>
+      <c r="R54" s="108" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="127" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B51" s="127" t="n"/>
-      <c r="C51" s="159" t="n"/>
-      <c r="D51" s="160" t="n"/>
-      <c r="E51" s="159" t="n"/>
-      <c r="F51" s="108" t="n"/>
-      <c r="G51" s="159" t="n"/>
-      <c r="H51" s="130" t="n">
-        <v>236.66</v>
-      </c>
-      <c r="I51" s="130" t="n">
-        <v>11.333</v>
-      </c>
-      <c r="J51" s="130" t="n">
-        <v>254.69</v>
-      </c>
-      <c r="K51" s="130" t="n">
-        <v>477.42</v>
-      </c>
-      <c r="L51" s="131" t="n">
-        <v>0.6234</v>
-      </c>
-      <c r="M51" s="159" t="n"/>
-      <c r="N51" s="161" t="n"/>
-      <c r="O51" s="159" t="n"/>
-      <c r="P51" s="159" t="n"/>
-      <c r="Q51" s="160" t="n"/>
-      <c r="R51" s="160" t="n"/>
-    </row>
-    <row r="55">
-      <c r="U55" s="98" t="n">
+      <c r="B55" s="127" t="n"/>
+      <c r="C55" s="159" t="n"/>
+      <c r="D55" s="160" t="n"/>
+      <c r="E55" s="159" t="n"/>
+      <c r="F55" s="108" t="n"/>
+      <c r="G55" s="159" t="n"/>
+      <c r="H55" s="130">
+        <f>SUM(H20:H53)</f>
+        <v/>
+      </c>
+      <c r="I55" s="130">
+        <f>SUM(I20:I53)</f>
+        <v/>
+      </c>
+      <c r="J55" s="130">
+        <f>SUM(J20:J53)</f>
+        <v/>
+      </c>
+      <c r="K55" s="130">
+        <f>SUM(K20:K53)</f>
+        <v/>
+      </c>
+      <c r="L55" s="131">
+        <f>AVERAGE(L20:L53)</f>
+        <v/>
+      </c>
+      <c r="M55" s="159" t="n"/>
+      <c r="N55" s="161" t="n"/>
+      <c r="O55" s="159" t="n"/>
+      <c r="P55" s="159" t="n"/>
+      <c r="Q55" s="160" t="n"/>
+      <c r="R55" s="160" t="n"/>
+    </row>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59">
+      <c r="U59" s="98" t="n">
         <v>0.1</v>
       </c>
-      <c r="V55" s="162" t="n">
+      <c r="V59" s="162" t="n">
         <v>0.14</v>
       </c>
-      <c r="W55" s="98">
+      <c r="W59" s="98">
         <f>U36*V36</f>
         <v/>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="163" t="n"/>
-      <c r="C56" s="164" t="n"/>
-      <c r="D56" s="164" t="n"/>
-      <c r="E56" s="165" t="n"/>
-      <c r="F56" s="164" t="n"/>
-      <c r="G56" s="166" t="n"/>
-      <c r="U56" s="98" t="n">
+    <row r="60">
+      <c r="B60" s="163" t="n"/>
+      <c r="C60" s="164" t="n"/>
+      <c r="D60" s="164" t="n"/>
+      <c r="E60" s="165" t="n"/>
+      <c r="F60" s="164" t="n"/>
+      <c r="G60" s="166" t="n"/>
+      <c r="U60" s="98" t="n">
         <v>0.9</v>
       </c>
-      <c r="V56" s="162" t="n">
+      <c r="V60" s="162" t="n">
         <v>0.02</v>
       </c>
-      <c r="W56" s="98">
+      <c r="W60" s="98">
         <f>U37*V37</f>
         <v/>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="163" t="n"/>
-      <c r="C57" s="164" t="n"/>
-      <c r="D57" s="164" t="n"/>
-      <c r="E57" s="165" t="n"/>
-      <c r="F57" s="164" t="n"/>
-      <c r="G57" s="166" t="n"/>
-      <c r="W57" s="98">
+    <row r="61">
+      <c r="B61" s="163" t="n"/>
+      <c r="C61" s="164" t="n"/>
+      <c r="D61" s="164" t="n"/>
+      <c r="E61" s="165" t="n"/>
+      <c r="F61" s="164" t="n"/>
+      <c r="G61" s="166" t="n"/>
+      <c r="W61" s="98">
         <f>W36+W37</f>
         <v/>
       </c>
@@ -11597,7 +11865,7 @@
       </c>
       <c r="T16" s="108" t="inlineStr">
         <is>
-          <t>Drew 01/08/25, 12-month term. NOT redeemed — past maturity 31/07/26, default / extension underway; model runs to 31/07/27. REL Lendco 4 / GB Bank; REL holds the mezz £2.05m of an £8.2m whole loan.</t>
+          <t>Drew 01/08/25, 12-month term. NOT redeemed — past maturity 31/07/26. Extension documented by Osborne Clarke; chased 15/09, still awaiting a substantive response from Forsters. REL Lendco 4 / GB Bank; REL mezz £2.05m of an £8.2m whole loan.</t>
         </is>
       </c>
       <c r="U16" s="195" t="inlineStr">
@@ -11693,7 +11961,7 @@
       </c>
       <c r="T17" s="108" t="inlineStr">
         <is>
-          <t>Drew 17/09/25, 15-month term to 17/03/27. Amortising via unit sales, whole-loan balance £12.04m. REL Lendco 5 / Oak North; REL mezz £4.39m, current balance £3.195m.</t>
+          <t>Drew 17/09/25, 15-month term to 17/03/27. COVENANT BREACH — cure period extended to 28/09/26 by Oak North. Curing via long-leasehold transfers: 70 Echinops and 101 Zinnia completed, Rhododendron sale approved at 92% of MV on 16/09. REL Lendco 5 / Oak North; REL mezz £4.39m, current balance £3.195m.</t>
         </is>
       </c>
       <c r="U17" s="195" t="inlineStr">

--- a/Deals_Sheet_REL.xlsx
+++ b/Deals_Sheet_REL.xlsx
@@ -197,7 +197,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="197">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -782,6 +782,9 @@
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1037,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W61"/>
+  <dimension ref="A1:W63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14.29" customWidth="1" style="98" min="1" max="1"/>
@@ -2806,7 +2809,7 @@
       </c>
       <c r="R35" s="108" t="inlineStr">
         <is>
-          <t>TS signed + £15k commitment fee paid; net £10.02m, 11%, 9m. City Financial Mortgages. -&gt; legals, ~early-Sept completion.</t>
+          <t>TS signed + £15k commitment fee paid; net £10.02m, 11%, 9m. City Financial Mortgages. -&gt; legals, ~early-Sept completion. 15/09 REL seeking back leverage from GB Bank on a loan-on-loan basis; sub-charge required, fee quote requested from Shepherd &amp; Wedderburn.</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3126,7 @@
       <c r="N40" s="124" t="n"/>
       <c r="O40" s="125" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="P40" s="120" t="inlineStr">
@@ -3138,7 +3141,7 @@
       </c>
       <c r="R40" s="108" t="inlineStr">
         <is>
-          <t>TS sent 10/09; awaiting countersigned term sheet and commitment fee.</t>
+          <t>TS sent 10/09; awaiting countersigned term sheet and commitment fee. TS issued 10/09 to Greengate (Anthony) and GLPG (Nick Swerner); credit paper follows the countersigned TS and commitment fee.</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3419,7 @@
       </c>
       <c r="R44" s="108" t="inlineStr">
         <is>
-          <t>TS issued. 10/09 broker asked for the full term sheet and advisors; 11/09 REL to send and confirm. Legal fees to stay proportionate to a small loan.</t>
+          <t>TS issued. 10/09 broker asked for the full term sheet and advisors; 11/09 REL to send and confirm. Legal fees to stay proportionate to a small loan. 14/09 draft TS sent to Jason Green (LS Capital); awaiting full borrower details, group structure chart and the security list.</t>
         </is>
       </c>
     </row>
@@ -4023,105 +4026,234 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="155" t="n"/>
-      <c r="B54" s="108" t="n"/>
-      <c r="C54" s="120" t="n"/>
-      <c r="D54" s="108" t="n"/>
-      <c r="E54" s="120" t="n"/>
-      <c r="F54" s="120" t="n"/>
-      <c r="G54" s="120" t="n"/>
-      <c r="H54" s="121" t="n"/>
+      <c r="A54" s="197" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B54" s="108" t="inlineStr">
+        <is>
+          <t>7 Rigg Approach, Lea Bridge, London E10 7QN</t>
+        </is>
+      </c>
+      <c r="C54" s="120" t="inlineStr">
+        <is>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="D54" s="108" t="inlineStr">
+        <is>
+          <t>Halls Victoria (Tanbir Rahman)</t>
+        </is>
+      </c>
+      <c r="E54" s="120" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="F54" s="120" t="inlineStr">
+        <is>
+          <t>Bridge</t>
+        </is>
+      </c>
+      <c r="G54" s="120" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H54" s="121" t="n">
+        <v>17.625</v>
+      </c>
       <c r="I54" s="122" t="n"/>
       <c r="J54" s="121" t="n"/>
-      <c r="K54" s="121" t="n"/>
-      <c r="L54" s="123" t="n"/>
-      <c r="M54" s="120" t="n"/>
+      <c r="K54" s="121" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="L54" s="123" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M54" s="120" t="n">
+        <v>18</v>
+      </c>
       <c r="N54" s="124" t="n"/>
-      <c r="O54" s="125" t="n"/>
-      <c r="P54" s="120" t="n"/>
-      <c r="Q54" s="108" t="n"/>
-      <c r="R54" s="108" t="n"/>
+      <c r="O54" s="125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P54" s="120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q54" s="108" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="R54" s="108" t="inlineStr">
+        <is>
+          <t>Enquiry 16/09 via Roscap (Suleman Rafiq), exclusively mandated. £23.5m purchase price, 2.12-acre freehold on Lea Bridge Road, Waltham Forest. Requested net day-one £17.625m (75% of PP) or max leverage, 18-24m, interest and fees fully rolled up, first charge. Planning play: DPA signed, indicative 531 co-living beds + 112 affordable + industrial. Exit is a sale post-consent; sponsor says an LOI is imminent from an HGP-backed developer at £45m subject to planning. Vendor deferral £5.875m to be subordinated. Valuation is Glenny Apr-2022 at £23.35m VP - stale, fresh lender-instructed val needed. Gross loan TBC. Next: decide whether to price. Came to Sumeer only.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="127" t="inlineStr">
+      <c r="A55" s="197" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B55" s="108" t="inlineStr">
+        <is>
+          <t>Project Bloom (codename) - Sixth Street bridge</t>
+        </is>
+      </c>
+      <c r="C55" s="120" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="D55" s="108" t="inlineStr">
+        <is>
+          <t>TBC (via Axis Capital Advisors)</t>
+        </is>
+      </c>
+      <c r="E55" s="120" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="F55" s="120" t="inlineStr">
+        <is>
+          <t>Bridge</t>
+        </is>
+      </c>
+      <c r="G55" s="120" t="inlineStr">
+        <is>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="H55" s="121" t="n"/>
+      <c r="I55" s="122" t="n"/>
+      <c r="J55" s="121" t="n"/>
+      <c r="K55" s="121" t="n"/>
+      <c r="L55" s="123" t="n"/>
+      <c r="M55" s="120" t="n"/>
+      <c r="N55" s="124" t="n"/>
+      <c r="O55" s="125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P55" s="120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q55" s="108" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="R55" s="108" t="inlineStr">
+        <is>
+          <t>Sumeer opened 17/08 with Axis Capital Advisors (Elliot Blatt). REL would participate alongside a co-lender and proposed Westbrook Partners. Sixth Street NDA carries a non-negotiable non-circumvent; Westbrook executed 10/09 and Axis released the Financing IM and loan model to both. Codename, so check figures against existing rows before treating as new. All figures TBC until the IM is read. Next: read the IM and model, then decide the size of participation. Came to Sumeer and Tashin only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="155" t="n"/>
+      <c r="B56" s="108" t="n"/>
+      <c r="C56" s="120" t="n"/>
+      <c r="D56" s="108" t="n"/>
+      <c r="E56" s="120" t="n"/>
+      <c r="F56" s="120" t="n"/>
+      <c r="G56" s="120" t="n"/>
+      <c r="H56" s="121" t="n"/>
+      <c r="I56" s="122" t="n"/>
+      <c r="J56" s="121" t="n"/>
+      <c r="K56" s="121" t="n"/>
+      <c r="L56" s="123" t="n"/>
+      <c r="M56" s="120" t="n"/>
+      <c r="N56" s="124" t="n"/>
+      <c r="O56" s="125" t="n"/>
+      <c r="P56" s="120" t="n"/>
+      <c r="Q56" s="108" t="n"/>
+      <c r="R56" s="108" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="127" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B55" s="127" t="n"/>
-      <c r="C55" s="159" t="n"/>
-      <c r="D55" s="160" t="n"/>
-      <c r="E55" s="159" t="n"/>
-      <c r="F55" s="108" t="n"/>
-      <c r="G55" s="159" t="n"/>
-      <c r="H55" s="130">
-        <f>SUM(H20:H53)</f>
+      <c r="B57" s="127" t="n"/>
+      <c r="C57" s="159" t="n"/>
+      <c r="D57" s="160" t="n"/>
+      <c r="E57" s="159" t="n"/>
+      <c r="F57" s="108" t="n"/>
+      <c r="G57" s="159" t="n"/>
+      <c r="H57" s="130">
+        <f>SUM(H20:H55)</f>
         <v/>
       </c>
-      <c r="I55" s="130">
-        <f>SUM(I20:I53)</f>
+      <c r="I57" s="130">
+        <f>SUM(I20:I55)</f>
         <v/>
       </c>
-      <c r="J55" s="130">
-        <f>SUM(J20:J53)</f>
+      <c r="J57" s="130">
+        <f>SUM(J20:J55)</f>
         <v/>
       </c>
-      <c r="K55" s="130">
-        <f>SUM(K20:K53)</f>
+      <c r="K57" s="130">
+        <f>SUM(K20:K55)</f>
         <v/>
       </c>
-      <c r="L55" s="131">
-        <f>AVERAGE(L20:L53)</f>
+      <c r="L57" s="131">
+        <f>AVERAGE(L20:L55)</f>
         <v/>
       </c>
-      <c r="M55" s="159" t="n"/>
-      <c r="N55" s="161" t="n"/>
-      <c r="O55" s="159" t="n"/>
-      <c r="P55" s="159" t="n"/>
-      <c r="Q55" s="160" t="n"/>
-      <c r="R55" s="160" t="n"/>
-    </row>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59">
-      <c r="U59" s="98" t="n">
+      <c r="M57" s="159" t="n"/>
+      <c r="N57" s="161" t="n"/>
+      <c r="O57" s="159" t="n"/>
+      <c r="P57" s="159" t="n"/>
+      <c r="Q57" s="160" t="n"/>
+      <c r="R57" s="160" t="n"/>
+    </row>
+    <row r="61">
+      <c r="U61" s="98" t="n">
         <v>0.1</v>
       </c>
-      <c r="V59" s="162" t="n">
+      <c r="V61" s="162" t="n">
         <v>0.14</v>
       </c>
-      <c r="W59" s="98">
+      <c r="W61" s="98">
         <f>U36*V36</f>
         <v/>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="163" t="n"/>
-      <c r="C60" s="164" t="n"/>
-      <c r="D60" s="164" t="n"/>
-      <c r="E60" s="165" t="n"/>
-      <c r="F60" s="164" t="n"/>
-      <c r="G60" s="166" t="n"/>
-      <c r="U60" s="98" t="n">
+    <row r="62">
+      <c r="B62" s="163" t="n"/>
+      <c r="C62" s="164" t="n"/>
+      <c r="D62" s="164" t="n"/>
+      <c r="E62" s="165" t="n"/>
+      <c r="F62" s="164" t="n"/>
+      <c r="G62" s="166" t="n"/>
+      <c r="U62" s="98" t="n">
         <v>0.9</v>
       </c>
-      <c r="V60" s="162" t="n">
+      <c r="V62" s="162" t="n">
         <v>0.02</v>
       </c>
-      <c r="W60" s="98">
+      <c r="W62" s="98">
         <f>U37*V37</f>
         <v/>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="163" t="n"/>
-      <c r="C61" s="164" t="n"/>
-      <c r="D61" s="164" t="n"/>
-      <c r="E61" s="165" t="n"/>
-      <c r="F61" s="164" t="n"/>
-      <c r="G61" s="166" t="n"/>
-      <c r="W61" s="98">
+    <row r="63">
+      <c r="B63" s="163" t="n"/>
+      <c r="C63" s="164" t="n"/>
+      <c r="D63" s="164" t="n"/>
+      <c r="E63" s="165" t="n"/>
+      <c r="F63" s="164" t="n"/>
+      <c r="G63" s="166" t="n"/>
+      <c r="W63" s="98">
         <f>W36+W37</f>
         <v/>
       </c>

--- a/Deals_Sheet_REL.xlsx
+++ b/Deals_Sheet_REL.xlsx
@@ -1040,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W63"/>
+  <dimension ref="A1:W64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14.29" customWidth="1" style="98" min="1" max="1"/>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="R40" s="108" t="inlineStr">
         <is>
-          <t>TS sent 10/09; awaiting countersigned term sheet and commitment fee. TS issued 10/09 to Greengate (Anthony) and GLPG (Nick Swerner); credit paper follows the countersigned TS and commitment fee.</t>
+          <t>TS sent 10/09; awaiting countersigned term sheet and commitment fee. TS issued 10/09 to Greengate (Anthony) and GLPG (Nick Swerner); credit paper follows the countersigned TS and commitment fee. 17/09 Nick Swerner (GLPG) asked to pick it up on Tuesday 22/09 - out of office Fri and Mon - so no countersigned TS or fee this week.</t>
         </is>
       </c>
     </row>
@@ -4158,91 +4158,142 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="155" t="n"/>
-      <c r="B56" s="108" t="n"/>
-      <c r="C56" s="120" t="n"/>
-      <c r="D56" s="108" t="n"/>
-      <c r="E56" s="120" t="n"/>
-      <c r="F56" s="120" t="n"/>
-      <c r="G56" s="120" t="n"/>
-      <c r="H56" s="121" t="n"/>
+      <c r="A56" s="197" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B56" s="108" t="inlineStr">
+        <is>
+          <t>Arlington Park - 2 blocks, PD conversion to resi</t>
+        </is>
+      </c>
+      <c r="C56" s="120" t="inlineStr">
+        <is>
+          <t>Office -&gt; Resi (PD conversion)</t>
+        </is>
+      </c>
+      <c r="D56" s="108" t="inlineStr">
+        <is>
+          <t>TBA SPV (via Omniya Reliance Capital)</t>
+        </is>
+      </c>
+      <c r="E56" s="120" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="F56" s="120" t="inlineStr">
+        <is>
+          <t>Development</t>
+        </is>
+      </c>
+      <c r="G56" s="120" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H56" s="121" t="n">
+        <v>14.8596</v>
+      </c>
       <c r="I56" s="122" t="n"/>
       <c r="J56" s="121" t="n"/>
-      <c r="K56" s="121" t="n"/>
+      <c r="K56" s="121" t="n">
+        <v>7.805</v>
+      </c>
       <c r="L56" s="123" t="n"/>
       <c r="M56" s="120" t="n"/>
       <c r="N56" s="124" t="n"/>
-      <c r="O56" s="125" t="n"/>
-      <c r="P56" s="120" t="n"/>
-      <c r="Q56" s="108" t="n"/>
-      <c r="R56" s="108" t="n"/>
+      <c r="O56" s="125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P56" s="120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q56" s="108" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="R56" s="108" t="inlineStr">
+        <is>
+          <t>Enquiry 17/09 via Inari Sharma (Omniya Reliance Capital), sent under the subject line of a calendar reply so it is easy to miss. Client has acquired Arlington Park - 362,589 sq ft NIA across 11 buildings on 39 acres - below MV in a bulk purchase, and wants to convert two blocks to residential under PD. Planning to be applied for within weeks, works intended from February. Figures for the two blocks: PP £7.805m, GDV £31.5m (100 units x 700 sq ft at £450/sq ft), build £9.24m incl 10% contingency (£120/sq ft), current debt £5.6196m at 72% of PP. Seeking £14.8596m net in total, exit by refinance. Loan to GDV 47%; LTV is left blank because against a £7.805m purchase price it would read 190% and mean nothing on a development facility. MV said to be over 25% above PP but no figure given, and no term stated. Borrower is a UK resident, ILR due Oct 2027, lends with Handelsbanken, Mizrahi and Shawbrook; in-house team, JCT with a tendered contractor. Rental income quoted at £30/sq ft = £2.1m appears to be the whole site, not the two blocks - worth clarifying. Full appraisals to follow. Broker asked for indicative rates and appetite. Next: decide appetite for a development/conversion facility at this size.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="127" t="inlineStr">
+      <c r="A57" s="155" t="n"/>
+      <c r="B57" s="108" t="n"/>
+      <c r="C57" s="120" t="n"/>
+      <c r="D57" s="108" t="n"/>
+      <c r="E57" s="120" t="n"/>
+      <c r="F57" s="120" t="n"/>
+      <c r="G57" s="120" t="n"/>
+      <c r="H57" s="121" t="n"/>
+      <c r="I57" s="122" t="n"/>
+      <c r="J57" s="121" t="n"/>
+      <c r="K57" s="121" t="n"/>
+      <c r="L57" s="123" t="n"/>
+      <c r="M57" s="120" t="n"/>
+      <c r="N57" s="124" t="n"/>
+      <c r="O57" s="125" t="n"/>
+      <c r="P57" s="120" t="n"/>
+      <c r="Q57" s="108" t="n"/>
+      <c r="R57" s="108" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="127" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B57" s="127" t="n"/>
-      <c r="C57" s="159" t="n"/>
-      <c r="D57" s="160" t="n"/>
-      <c r="E57" s="159" t="n"/>
-      <c r="F57" s="108" t="n"/>
-      <c r="G57" s="159" t="n"/>
-      <c r="H57" s="130">
-        <f>SUM(H20:H55)</f>
+      <c r="B58" s="127" t="n"/>
+      <c r="C58" s="159" t="n"/>
+      <c r="D58" s="160" t="n"/>
+      <c r="E58" s="159" t="n"/>
+      <c r="F58" s="108" t="n"/>
+      <c r="G58" s="159" t="n"/>
+      <c r="H58" s="130">
+        <f>SUM(H20:H56)</f>
         <v/>
       </c>
-      <c r="I57" s="130">
-        <f>SUM(I20:I55)</f>
+      <c r="I58" s="130">
+        <f>SUM(I20:I56)</f>
         <v/>
       </c>
-      <c r="J57" s="130">
-        <f>SUM(J20:J55)</f>
+      <c r="J58" s="130">
+        <f>SUM(J20:J56)</f>
         <v/>
       </c>
-      <c r="K57" s="130">
-        <f>SUM(K20:K55)</f>
+      <c r="K58" s="130">
+        <f>SUM(K20:K56)</f>
         <v/>
       </c>
-      <c r="L57" s="131">
-        <f>AVERAGE(L20:L55)</f>
+      <c r="L58" s="131">
+        <f>AVERAGE(L20:L56)</f>
         <v/>
       </c>
-      <c r="M57" s="159" t="n"/>
-      <c r="N57" s="161" t="n"/>
-      <c r="O57" s="159" t="n"/>
-      <c r="P57" s="159" t="n"/>
-      <c r="Q57" s="160" t="n"/>
-      <c r="R57" s="160" t="n"/>
-    </row>
-    <row r="61">
-      <c r="U61" s="98" t="n">
+      <c r="M58" s="159" t="n"/>
+      <c r="N58" s="161" t="n"/>
+      <c r="O58" s="159" t="n"/>
+      <c r="P58" s="159" t="n"/>
+      <c r="Q58" s="160" t="n"/>
+      <c r="R58" s="160" t="n"/>
+    </row>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62">
+      <c r="U62" s="98" t="n">
         <v>0.1</v>
       </c>
-      <c r="V61" s="162" t="n">
+      <c r="V62" s="162" t="n">
         <v>0.14</v>
       </c>
-      <c r="W61" s="98">
+      <c r="W62" s="98">
         <f>U36*V36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="163" t="n"/>
-      <c r="C62" s="164" t="n"/>
-      <c r="D62" s="164" t="n"/>
-      <c r="E62" s="165" t="n"/>
-      <c r="F62" s="164" t="n"/>
-      <c r="G62" s="166" t="n"/>
-      <c r="U62" s="98" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V62" s="162" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W62" s="98">
-        <f>U37*V37</f>
         <v/>
       </c>
     </row>
@@ -4253,7 +4304,25 @@
       <c r="E63" s="165" t="n"/>
       <c r="F63" s="164" t="n"/>
       <c r="G63" s="166" t="n"/>
+      <c r="U63" s="98" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V63" s="162" t="n">
+        <v>0.02</v>
+      </c>
       <c r="W63" s="98">
+        <f>U37*V37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="163" t="n"/>
+      <c r="C64" s="164" t="n"/>
+      <c r="D64" s="164" t="n"/>
+      <c r="E64" s="165" t="n"/>
+      <c r="F64" s="164" t="n"/>
+      <c r="G64" s="166" t="n"/>
+      <c r="W64" s="98">
         <f>W36+W37</f>
         <v/>
       </c>

--- a/Deals_Sheet_REL.xlsx
+++ b/Deals_Sheet_REL.xlsx
@@ -197,7 +197,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="199">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -784,6 +784,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -1040,7 +1043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W64"/>
+  <dimension ref="A1:W65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14.29" customWidth="1" style="98" min="1" max="1"/>
@@ -3141,7 +3144,7 @@
       </c>
       <c r="R40" s="108" t="inlineStr">
         <is>
-          <t>TS sent 10/09; awaiting countersigned term sheet and commitment fee. TS issued 10/09 to Greengate (Anthony) and GLPG (Nick Swerner); credit paper follows the countersigned TS and commitment fee. 17/09 Nick Swerner (GLPG) asked to pick it up on Tuesday 22/09 - out of office Fri and Mon - so no countersigned TS or fee this week.</t>
+          <t>TS sent 10/09; awaiting countersigned term sheet and commitment fee. TS issued 10/09 to Greengate (Anthony) and GLPG (Nick Swerner); credit paper follows the countersigned TS and commitment fee. 17/09 Nick Swerner (GLPG) asked to pick it up on Tuesday 22/09 - out of office Fri and Mon - so no countersigned TS or fee this week. 18/09 Sumeer offered 11am or 2-4pm on Tuesday 22/09.</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3498,7 @@
       </c>
       <c r="R45" s="108" t="inlineStr">
         <is>
-          <t>Updated terms 08/09: £13.5m, 12 months plus a 6-month extension option. 12/09 broker pushing on pricing; REL holding position ahead of formal IC approval.</t>
+          <t>Updated terms 08/09: £13.5m, 12 months plus a 6-month extension option. 12/09 broker pushing on pricing; REL holding position ahead of formal IC approval. 18/09 chased Mantra again for the borrower's feedback; still nothing back.</t>
         </is>
       </c>
     </row>
@@ -4027,21 +4030,21 @@
     </row>
     <row r="54">
       <c r="A54" s="197" t="n">
-        <v>46266</v>
+        <v>46235</v>
       </c>
       <c r="B54" s="108" t="inlineStr">
         <is>
-          <t>7 Rigg Approach, Lea Bridge, London E10 7QN</t>
+          <t>Project Bloom (codename) - Sixth Street bridge</t>
         </is>
       </c>
       <c r="C54" s="120" t="inlineStr">
         <is>
-          <t>Land</t>
+          <t>TBC</t>
         </is>
       </c>
       <c r="D54" s="108" t="inlineStr">
         <is>
-          <t>Halls Victoria (Tanbir Rahman)</t>
+          <t>TBC (via Axis Capital Advisors)</t>
         </is>
       </c>
       <c r="E54" s="120" t="inlineStr">
@@ -4056,23 +4059,15 @@
       </c>
       <c r="G54" s="120" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H54" s="121" t="n">
-        <v>17.625</v>
-      </c>
+          <t>TBC</t>
+        </is>
+      </c>
+      <c r="H54" s="121" t="n"/>
       <c r="I54" s="122" t="n"/>
       <c r="J54" s="121" t="n"/>
-      <c r="K54" s="121" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="L54" s="123" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M54" s="120" t="n">
-        <v>18</v>
-      </c>
+      <c r="K54" s="121" t="n"/>
+      <c r="L54" s="123" t="n"/>
+      <c r="M54" s="120" t="n"/>
       <c r="N54" s="124" t="n"/>
       <c r="O54" s="125" t="inlineStr">
         <is>
@@ -4091,27 +4086,27 @@
       </c>
       <c r="R54" s="108" t="inlineStr">
         <is>
-          <t>Enquiry 16/09 via Roscap (Suleman Rafiq), exclusively mandated. £23.5m purchase price, 2.12-acre freehold on Lea Bridge Road, Waltham Forest. Requested net day-one £17.625m (75% of PP) or max leverage, 18-24m, interest and fees fully rolled up, first charge. Planning play: DPA signed, indicative 531 co-living beds + 112 affordable + industrial. Exit is a sale post-consent; sponsor says an LOI is imminent from an HGP-backed developer at £45m subject to planning. Vendor deferral £5.875m to be subordinated. Valuation is Glenny Apr-2022 at £23.35m VP - stale, fresh lender-instructed val needed. Gross loan TBC. Next: decide whether to price. Came to Sumeer only.</t>
+          <t>Sumeer opened 17/08 with Axis Capital Advisors (Elliot Blatt). REL would participate alongside a co-lender and proposed Westbrook Partners. Sixth Street NDA carries a non-negotiable non-circumvent; Westbrook executed 10/09 and Axis released the Financing IM and loan model to both. Codename, so check figures against existing rows before treating as new. All figures TBC until the IM is read. Next: read the IM and model, then decide the size of participation. Came to Sumeer and Tashin only.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="197" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
       <c r="B55" s="108" t="inlineStr">
         <is>
-          <t>Project Bloom (codename) - Sixth Street bridge</t>
+          <t>Arlington Park - 2 blocks, PD conversion to resi</t>
         </is>
       </c>
       <c r="C55" s="120" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Office -&gt; Resi (PD conversion)</t>
         </is>
       </c>
       <c r="D55" s="108" t="inlineStr">
         <is>
-          <t>TBC (via Axis Capital Advisors)</t>
+          <t>TBA SPV (via Omniya Reliance Capital)</t>
         </is>
       </c>
       <c r="E55" s="120" t="inlineStr">
@@ -4121,18 +4116,22 @@
       </c>
       <c r="F55" s="120" t="inlineStr">
         <is>
-          <t>Bridge</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="G55" s="120" t="inlineStr">
         <is>
-          <t>TBC</t>
-        </is>
-      </c>
-      <c r="H55" s="121" t="n"/>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H55" s="121" t="n">
+        <v>14.8596</v>
+      </c>
       <c r="I55" s="122" t="n"/>
       <c r="J55" s="121" t="n"/>
-      <c r="K55" s="121" t="n"/>
+      <c r="K55" s="121" t="n">
+        <v>7.805</v>
+      </c>
       <c r="L55" s="123" t="n"/>
       <c r="M55" s="120" t="n"/>
       <c r="N55" s="124" t="n"/>
@@ -4153,7 +4152,7 @@
       </c>
       <c r="R55" s="108" t="inlineStr">
         <is>
-          <t>Sumeer opened 17/08 with Axis Capital Advisors (Elliot Blatt). REL would participate alongside a co-lender and proposed Westbrook Partners. Sixth Street NDA carries a non-negotiable non-circumvent; Westbrook executed 10/09 and Axis released the Financing IM and loan model to both. Codename, so check figures against existing rows before treating as new. All figures TBC until the IM is read. Next: read the IM and model, then decide the size of participation. Came to Sumeer and Tashin only.</t>
+          <t>Enquiry 17/09 via Inari Sharma (Omniya Reliance Capital), sent under the subject line of a calendar reply so it is easy to miss. Client has acquired Arlington Park - 362,589 sq ft NIA across 11 buildings on 39 acres - below MV in a bulk purchase, and wants to convert two blocks to residential under PD. Planning to be applied for within weeks, works intended from February. Figures for the two blocks: PP £7.805m, GDV £31.5m (100 units x 700 sq ft at £450/sq ft), build £9.24m incl 10% contingency (£120/sq ft), current debt £5.6196m at 72% of PP. Seeking £14.8596m net in total, exit by refinance. Loan to GDV 47%; LTV is left blank because against a £7.805m purchase price it would read 190% and mean nothing on a development facility. MV said to be over 25% above PP but no figure given, and no term stated. Borrower is a UK resident, ILR due Oct 2027, lends with Handelsbanken, Mizrahi and Shawbrook; in-house team, JCT with a tendered contractor. Rental income quoted at £30/sq ft = £2.1m appears to be the whole site, not the two blocks - worth clarifying. Full appraisals to follow. Broker asked for indicative rates and appetite. Next: decide appetite for a development/conversion facility at this size.</t>
         </is>
       </c>
     </row>
@@ -4163,17 +4162,17 @@
       </c>
       <c r="B56" s="108" t="inlineStr">
         <is>
-          <t>Arlington Park - 2 blocks, PD conversion to resi</t>
+          <t>Project Meridian - 4 UK hotels (London/Essex, Aberdeen, Sheffield)</t>
         </is>
       </c>
       <c r="C56" s="120" t="inlineStr">
         <is>
-          <t>Office -&gt; Resi (PD conversion)</t>
+          <t>Hotel</t>
         </is>
       </c>
       <c r="D56" s="108" t="inlineStr">
         <is>
-          <t>TBA SPV (via Omniya Reliance Capital)</t>
+          <t>TBC (via PAC Advisors)</t>
         </is>
       </c>
       <c r="E56" s="120" t="inlineStr">
@@ -4183,24 +4182,28 @@
       </c>
       <c r="F56" s="120" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Term</t>
         </is>
       </c>
       <c r="G56" s="120" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H56" s="121" t="n">
-        <v>14.8596</v>
-      </c>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H56" s="121" t="n"/>
       <c r="I56" s="122" t="n"/>
-      <c r="J56" s="121" t="n"/>
+      <c r="J56" s="121" t="n">
+        <v>16.5</v>
+      </c>
       <c r="K56" s="121" t="n">
-        <v>7.805</v>
-      </c>
-      <c r="L56" s="123" t="n"/>
-      <c r="M56" s="120" t="n"/>
+        <v>27.65</v>
+      </c>
+      <c r="L56" s="123" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="M56" s="120" t="n">
+        <v>60</v>
+      </c>
       <c r="N56" s="124" t="n"/>
       <c r="O56" s="125" t="inlineStr">
         <is>
@@ -4219,99 +4222,151 @@
       </c>
       <c r="R56" s="108" t="inlineStr">
         <is>
-          <t>Enquiry 17/09 via Inari Sharma (Omniya Reliance Capital), sent under the subject line of a calendar reply so it is easy to miss. Client has acquired Arlington Park - 362,589 sq ft NIA across 11 buildings on 39 acres - below MV in a bulk purchase, and wants to convert two blocks to residential under PD. Planning to be applied for within weeks, works intended from February. Figures for the two blocks: PP £7.805m, GDV £31.5m (100 units x 700 sq ft at £450/sq ft), build £9.24m incl 10% contingency (£120/sq ft), current debt £5.6196m at 72% of PP. Seeking £14.8596m net in total, exit by refinance. Loan to GDV 47%; LTV is left blank because against a £7.805m purchase price it would read 190% and mean nothing on a development facility. MV said to be over 25% above PP but no figure given, and no term stated. Borrower is a UK resident, ILR due Oct 2027, lends with Handelsbanken, Mizrahi and Shawbrook; in-house team, JCT with a tendered contractor. Rental income quoted at £30/sq ft = £2.1m appears to be the whole site, not the two blocks - worth clarifying. Full appraisals to follow. Broker asked for indicative rates and appetite. Next: decide appetite for a development/conversion facility at this size.</t>
+          <t>Enquiry 18/09 from Mike Allen, PAC Advisors (New York), direct to Tashin, who forwarded it as 'this looks interesting'. Acquisition of four operating economy/select-service hotels under a global brand: two in Greater London/Essex, one Aberdeen, one Sheffield. Mix of freehold, Scottish heritable title and long leasehold; real estate and operating businesses both inside the perimeter, so EBITDAR and EBITDA are materially the same. Seeking £16.5m senior secured. PP £27.65m, total uses £31.11m including costs and a £2.08m capex reserve, sponsor equity £14.61m = 47% of uses. LTC 53.0%, LTPP 59.7%. FY25/26 actuals: revenue £9.82m, EBITDAR £3.34m at a 34% margin, 12.1% yield on PP, 8.3x EBITDAR. Debt yield 20.2%, ICR 2.89x, DSCR 2.36x - but those coverage figures assume 7% over a FIVE-YEAR term with 12 months interest-only and 25-year amortisation, which is a different product from REL's bridge book and is the first thing to decide. Terms executed, initial seller payment made, DD complete, four acquisitions not interconditional. RICS valuations still to be instructed. Next: decide whether REL does five-year amortising term debt at all before spending time on it.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="155" t="n"/>
-      <c r="B57" s="108" t="n"/>
-      <c r="C57" s="120" t="n"/>
-      <c r="D57" s="108" t="n"/>
-      <c r="E57" s="120" t="n"/>
-      <c r="F57" s="120" t="n"/>
-      <c r="G57" s="120" t="n"/>
+      <c r="A57" s="197" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="108" t="inlineStr">
+        <is>
+          <t>Rookery Manor, Edingworth Rd, Weston-Super-Mare BS24 0JB</t>
+        </is>
+      </c>
+      <c r="C57" s="120" t="inlineStr">
+        <is>
+          <t>Leisure</t>
+        </is>
+      </c>
+      <c r="D57" s="108" t="inlineStr">
+        <is>
+          <t>IKC Assets Limited (Ian Clapp)</t>
+        </is>
+      </c>
+      <c r="E57" s="120" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="F57" s="120" t="inlineStr">
+        <is>
+          <t>Bridge</t>
+        </is>
+      </c>
+      <c r="G57" s="120" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="H57" s="121" t="n"/>
       <c r="I57" s="122" t="n"/>
-      <c r="J57" s="121" t="n"/>
-      <c r="K57" s="121" t="n"/>
-      <c r="L57" s="123" t="n"/>
-      <c r="M57" s="120" t="n"/>
+      <c r="J57" s="121" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K57" s="121" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L57" s="123" t="n">
+        <v>0.6034</v>
+      </c>
+      <c r="M57" s="120" t="n">
+        <v>12</v>
+      </c>
       <c r="N57" s="124" t="n"/>
-      <c r="O57" s="125" t="n"/>
-      <c r="P57" s="120" t="n"/>
-      <c r="Q57" s="108" t="n"/>
-      <c r="R57" s="108" t="n"/>
+      <c r="O57" s="125" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P57" s="120" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q57" s="108" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="R57" s="108" t="inlineStr">
+        <is>
+          <t>Enquiry 18/09 from Zara Akbar, Thalia Partners, following a meeting with Sumeer on 17/09. Borrower IKC Assets Limited (Ian Clapp). Rookery Manor, Edingworth Road, Weston-Super-Mare BS24 0JB - c.16.8 acres, events venue with lodges. Value £5.8m supported by recent Knight Frank and Eddisons valuations, both attached. £3.5m sought to consolidate existing facilities into one loan and buy time for a longer-term exit; ideally 12 months with flexibility to 24. First legal charge plus security over the UK companies. LTV 60%. Rookery Manor Limited was profitable in 2025; £428k spent in 2026 converting six more cottages; residential planning consent for nine houses valued at £450k each by Greenslade Taylor Hunt, which the borrower may instead sell with outline permission. Full data room available. Next: ask for the data room and check whether the planning-consent value is a real exit or an option.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="127" t="inlineStr">
+      <c r="A58" s="155" t="n"/>
+      <c r="B58" s="108" t="n"/>
+      <c r="C58" s="120" t="n"/>
+      <c r="D58" s="108" t="n"/>
+      <c r="E58" s="120" t="n"/>
+      <c r="F58" s="120" t="n"/>
+      <c r="G58" s="120" t="n"/>
+      <c r="H58" s="121" t="n"/>
+      <c r="I58" s="122" t="n"/>
+      <c r="J58" s="121" t="n"/>
+      <c r="K58" s="121" t="n"/>
+      <c r="L58" s="123" t="n"/>
+      <c r="M58" s="120" t="n"/>
+      <c r="N58" s="124" t="n"/>
+      <c r="O58" s="125" t="n"/>
+      <c r="P58" s="120" t="n"/>
+      <c r="Q58" s="108" t="n"/>
+      <c r="R58" s="108" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="127" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B58" s="127" t="n"/>
-      <c r="C58" s="159" t="n"/>
-      <c r="D58" s="160" t="n"/>
-      <c r="E58" s="159" t="n"/>
-      <c r="F58" s="108" t="n"/>
-      <c r="G58" s="159" t="n"/>
-      <c r="H58" s="130">
-        <f>SUM(H20:H56)</f>
+      <c r="B59" s="127" t="n"/>
+      <c r="C59" s="159" t="n"/>
+      <c r="D59" s="160" t="n"/>
+      <c r="E59" s="159" t="n"/>
+      <c r="F59" s="108" t="n"/>
+      <c r="G59" s="159" t="n"/>
+      <c r="H59" s="130">
+        <f>SUM(H20:H57)</f>
         <v/>
       </c>
-      <c r="I58" s="130">
-        <f>SUM(I20:I56)</f>
+      <c r="I59" s="130">
+        <f>SUM(I20:I57)</f>
         <v/>
       </c>
-      <c r="J58" s="130">
-        <f>SUM(J20:J56)</f>
+      <c r="J59" s="130">
+        <f>SUM(J20:J57)</f>
         <v/>
       </c>
-      <c r="K58" s="130">
-        <f>SUM(K20:K56)</f>
+      <c r="K59" s="130">
+        <f>SUM(K20:K57)</f>
         <v/>
       </c>
-      <c r="L58" s="131">
-        <f>AVERAGE(L20:L56)</f>
+      <c r="L59" s="131">
+        <f>AVERAGE(L20:L57)</f>
         <v/>
       </c>
-      <c r="M58" s="159" t="n"/>
-      <c r="N58" s="161" t="n"/>
-      <c r="O58" s="159" t="n"/>
-      <c r="P58" s="159" t="n"/>
-      <c r="Q58" s="160" t="n"/>
-      <c r="R58" s="160" t="n"/>
-    </row>
-    <row r="59"/>
+      <c r="M59" s="159" t="n"/>
+      <c r="N59" s="161" t="n"/>
+      <c r="O59" s="159" t="n"/>
+      <c r="P59" s="159" t="n"/>
+      <c r="Q59" s="160" t="n"/>
+      <c r="R59" s="160" t="n"/>
+    </row>
     <row r="60"/>
     <row r="61"/>
-    <row r="62">
-      <c r="U62" s="98" t="n">
+    <row r="62"/>
+    <row r="63">
+      <c r="U63" s="98" t="n">
         <v>0.1</v>
       </c>
-      <c r="V62" s="162" t="n">
+      <c r="V63" s="162" t="n">
         <v>0.14</v>
       </c>
-      <c r="W62" s="98">
+      <c r="W63" s="98">
         <f>U36*V36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="163" t="n"/>
-      <c r="C63" s="164" t="n"/>
-      <c r="D63" s="164" t="n"/>
-      <c r="E63" s="165" t="n"/>
-      <c r="F63" s="164" t="n"/>
-      <c r="G63" s="166" t="n"/>
-      <c r="U63" s="98" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="V63" s="162" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W63" s="98">
-        <f>U37*V37</f>
         <v/>
       </c>
     </row>
@@ -4322,7 +4377,25 @@
       <c r="E64" s="165" t="n"/>
       <c r="F64" s="164" t="n"/>
       <c r="G64" s="166" t="n"/>
+      <c r="U64" s="98" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="V64" s="162" t="n">
+        <v>0.02</v>
+      </c>
       <c r="W64" s="98">
+        <f>U37*V37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="163" t="n"/>
+      <c r="C65" s="164" t="n"/>
+      <c r="D65" s="164" t="n"/>
+      <c r="E65" s="165" t="n"/>
+      <c r="F65" s="164" t="n"/>
+      <c r="G65" s="166" t="n"/>
+      <c r="W65" s="98">
         <f>W36+W37</f>
         <v/>
       </c>
@@ -4354,7 +4427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A3:V96"/>
+  <dimension ref="A3:V97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.70703125" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9.57" customWidth="1" style="98" min="1" max="1"/>
@@ -11037,63 +11110,134 @@
       </c>
     </row>
     <row r="95" ht="12.75" customFormat="1" customHeight="1" s="98">
-      <c r="A95" s="108" t="n"/>
-      <c r="B95" s="108" t="n"/>
-      <c r="C95" s="157" t="n"/>
-      <c r="D95" s="108" t="n"/>
-      <c r="E95" s="120" t="n"/>
-      <c r="F95" s="120" t="n"/>
-      <c r="G95" s="120" t="n"/>
-      <c r="H95" s="121" t="n"/>
-      <c r="I95" s="122" t="n"/>
-      <c r="J95" s="121" t="n"/>
-      <c r="K95" s="121" t="n"/>
-      <c r="L95" s="123" t="n"/>
-      <c r="M95" s="120" t="n"/>
-      <c r="N95" s="124" t="n"/>
-      <c r="O95" s="125" t="n"/>
-      <c r="P95" s="120" t="n"/>
-      <c r="Q95" s="108" t="n"/>
-      <c r="R95" s="108" t="n"/>
+      <c r="A95" s="198" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B95" s="190" t="inlineStr">
+        <is>
+          <t>7 Rigg Approach, Lea Bridge, London E10 7QN</t>
+        </is>
+      </c>
+      <c r="C95" s="183" t="inlineStr">
+        <is>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="D95" s="182" t="inlineStr">
+        <is>
+          <t>Halls Victoria (Tanbir Rahman)</t>
+        </is>
+      </c>
+      <c r="E95" s="183" t="inlineStr">
+        <is>
+          <t>Senior</t>
+        </is>
+      </c>
+      <c r="F95" s="183" t="inlineStr">
+        <is>
+          <t>Bridge</t>
+        </is>
+      </c>
+      <c r="G95" s="183" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H95" s="185" t="n">
+        <v>17.625</v>
+      </c>
+      <c r="I95" s="186" t="n"/>
+      <c r="J95" s="185" t="n"/>
+      <c r="K95" s="185" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="L95" s="187" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M95" s="183" t="n">
+        <v>18</v>
+      </c>
+      <c r="N95" s="188" t="n"/>
+      <c r="O95" s="189" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P95" s="183" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q95" s="184" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="R95" s="184" t="inlineStr">
+        <is>
+          <t>Declined by REL 18/09: for a planning-led transaction REL needs a meaningful level of hard equity invested, typically 30-40% of purchase price. Enquiry 16/09 via Roscap (exclusively mandated by Halls Victoria); £23.5m PP, £17.625m net day-one requested at 75% of PP, 18-24m rolled up. Came to Sumeer only.</t>
+        </is>
+      </c>
+      <c r="S95" s="158" t="n"/>
     </row>
     <row r="96" ht="12.75" customFormat="1" customHeight="1" s="98">
-      <c r="A96" s="127" t="inlineStr">
+      <c r="A96" s="108" t="n"/>
+      <c r="B96" s="108" t="n"/>
+      <c r="C96" s="157" t="n"/>
+      <c r="D96" s="108" t="n"/>
+      <c r="E96" s="120" t="n"/>
+      <c r="F96" s="120" t="n"/>
+      <c r="G96" s="120" t="n"/>
+      <c r="H96" s="121" t="n"/>
+      <c r="I96" s="122" t="n"/>
+      <c r="J96" s="121" t="n"/>
+      <c r="K96" s="121" t="n"/>
+      <c r="L96" s="123" t="n"/>
+      <c r="M96" s="120" t="n"/>
+      <c r="N96" s="124" t="n"/>
+      <c r="O96" s="125" t="n"/>
+      <c r="P96" s="120" t="n"/>
+      <c r="Q96" s="108" t="n"/>
+      <c r="R96" s="108" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="127" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B96" s="127" t="n"/>
-      <c r="C96" s="159" t="n"/>
-      <c r="D96" s="160" t="n"/>
-      <c r="E96" s="159" t="n"/>
-      <c r="F96" s="159" t="n"/>
-      <c r="G96" s="159" t="n"/>
-      <c r="H96" s="130">
-        <f>SUM(H5:H94)</f>
+      <c r="B97" s="127" t="n"/>
+      <c r="C97" s="159" t="n"/>
+      <c r="D97" s="160" t="n"/>
+      <c r="E97" s="159" t="n"/>
+      <c r="F97" s="159" t="n"/>
+      <c r="G97" s="159" t="n"/>
+      <c r="H97" s="130">
+        <f>SUM(H5:H95)</f>
         <v/>
       </c>
-      <c r="I96" s="130">
-        <f>SUM(I5:I94)</f>
+      <c r="I97" s="130">
+        <f>SUM(I5:I95)</f>
         <v/>
       </c>
-      <c r="J96" s="130">
-        <f>SUM(J5:J94)</f>
+      <c r="J97" s="130">
+        <f>SUM(J5:J95)</f>
         <v/>
       </c>
-      <c r="K96" s="130">
-        <f>SUM(K5:K94)</f>
+      <c r="K97" s="130">
+        <f>SUM(K5:K95)</f>
         <v/>
       </c>
-      <c r="L96" s="131">
-        <f>J96/K96</f>
+      <c r="L97" s="131">
+        <f>J97/K97</f>
         <v/>
       </c>
-      <c r="M96" s="159" t="n"/>
-      <c r="N96" s="161" t="n"/>
-      <c r="O96" s="159" t="n"/>
-      <c r="P96" s="159" t="n"/>
-      <c r="Q96" s="160" t="n"/>
-      <c r="R96" s="160" t="n"/>
+      <c r="M97" s="159" t="n"/>
+      <c r="N97" s="161" t="n"/>
+      <c r="O97" s="159" t="n"/>
+      <c r="P97" s="159" t="n"/>
+      <c r="Q97" s="160" t="n"/>
+      <c r="R97" s="160" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
